--- a/files/diet-data-contract-v1.0.1.xlsx
+++ b/files/diet-data-contract-v1.0.1.xlsx
@@ -7463,7 +7463,7 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>{지난 끼니}에 고기·생선·달걀·두부를 드셨나요?</t>
+    <t>{지난 끼니}에 단백질류(고기·생선·달걀 등)를 드셨나요?</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -23257,7 +23257,7 @@
   <sheetPr>
     <tabColor rgb="FF315A7D"/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1"/>
@@ -23504,6 +23504,28 @@
       </c>
       <c r="D26" s="16" t="s">
         <v>2507</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="28">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>단백질 질문 문장 (2026-10-07)</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>질문 DIET-Q-06 = 「{지난 끼니}에 고기·생선·달걀·두부를 드셨나요?」</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>질문 DIET-Q-06 = 「{지난 끼니}에 단백질류(고기·생선·달걀 등)를 드셨나요?」. 질문 버전은 1.0.0 그대로이며 선택지·점수는 바꾸지 않음</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>질문 DIET-Q-06 · 참조설정데이터</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/files/diet-data-contract-v1.0.1.xlsx
+++ b/files/diet-data-contract-v1.0.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A41867F9-B6C1-4CF1-8F11-1E0EE67A1198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1676964F-810D-412E-AAD7-D4794ADE8AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25313,6 +25313,10 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
+    <t>거의 못 먹거나 걸렀어요</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t>{끼니</t>
     </r>
@@ -25675,7 +25679,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>배는</t>
+      <t>배부름은</t>
     </r>
     <r>
       <rPr>
@@ -25694,7 +25698,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>어땠나요</t>
+      <t>어느</t>
     </r>
     <r>
       <rPr>
@@ -25704,6 +25708,25 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정도였나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">? </t>
     </r>
     <r>
@@ -25927,11 +25950,7 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>{지난 끼니}을 드신 뒤 배는 어땠나요?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>거의 못 먹거나 걸렀어요</t>
+    <t>{지난 끼니}을 드신 뒤 배부름은 어느 정도였나요?</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -26976,7 +26995,7 @@
         <v>2658</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>2666</v>
+        <v>2667</v>
       </c>
       <c r="D22" s="12" t="s">
         <v>2659</v>
@@ -58410,7 +58429,7 @@
         <v>849</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>850</v>
@@ -58617,7 +58636,7 @@
         <v>887</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>2668</v>
+        <v>2666</v>
       </c>
       <c r="F4" s="1">
         <v>-1</v>
@@ -60373,18 +60392,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -60406,18 +60425,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA5F7BAD-F7AB-4266-8370-535EF14A9159}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/files/diet-data-contract-v1.0.1.xlsx
+++ b/files/diet-data-contract-v1.0.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1676964F-810D-412E-AAD7-D4794ADE8AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88D6B5C7-D1D2-4D2C-8D5E-88DA9FD01540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25317,6 +25317,10 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
+    <t>{지난 끼니}을 드신 뒤 배부름은 어느 정도였나요?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t>{끼니</t>
     </r>
@@ -25375,7 +25379,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>반찬을</t>
+      <t>반찬은</t>
     </r>
     <r>
       <rPr>
@@ -25413,7 +25417,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>가지</t>
+      <t>가지였나요</t>
     </r>
     <r>
       <rPr>
@@ -25423,7 +25427,7 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t>? · {</t>
     </r>
     <r>
       <rPr>
@@ -25432,7 +25436,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>드셨나요</t>
+      <t>끼니</t>
     </r>
     <r>
       <rPr>
@@ -25442,6 +25446,120 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">} </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>음료</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>간식은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>몇</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번이었나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
       <t>? · {</t>
     </r>
     <r>
@@ -25470,7 +25588,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>전후로</t>
+      <t>후</t>
     </r>
     <r>
       <rPr>
@@ -25489,7 +25607,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>단</t>
+      <t>배부름은</t>
     </r>
     <r>
       <rPr>
@@ -25508,7 +25626,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>음료나</t>
+      <t>어땠나요</t>
     </r>
     <r>
       <rPr>
@@ -25518,7 +25636,7 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve">? </t>
     </r>
     <r>
       <rPr>
@@ -25527,7 +25645,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>간식을</t>
+      <t>등</t>
     </r>
     <r>
       <rPr>
@@ -25537,7 +25655,7 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve">. </t>
     </r>
     <r>
       <rPr>
@@ -25546,7 +25664,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>몇</t>
+      <t>끼니</t>
     </r>
     <r>
       <rPr>
@@ -25565,7 +25683,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>번</t>
+      <t>이름</t>
     </r>
     <r>
       <rPr>
@@ -25584,7 +25702,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>드셨나요</t>
+      <t>뒤</t>
     </r>
     <r>
       <rPr>
@@ -25594,7 +25712,7 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t>? · {</t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -25603,7 +25721,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>끼니</t>
+      <t>조사를</t>
     </r>
     <r>
       <rPr>
@@ -25613,7 +25731,7 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t>}</t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -25622,7 +25740,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>을</t>
+      <t>문장에</t>
     </r>
     <r>
       <rPr>
@@ -25641,7 +25759,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>드신</t>
+      <t>미리</t>
     </r>
     <r>
       <rPr>
@@ -25660,7 +25778,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>뒤</t>
+      <t>써</t>
     </r>
     <r>
       <rPr>
@@ -25679,7 +25797,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>배부름은</t>
+      <t>두고</t>
     </r>
     <r>
       <rPr>
@@ -25689,7 +25807,7 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve"> 32</t>
     </r>
     <r>
       <rPr>
@@ -25698,7 +25816,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>어느</t>
+      <t>자</t>
     </r>
     <r>
       <rPr>
@@ -25717,7 +25835,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>정도였나요</t>
+      <t>이내를</t>
     </r>
     <r>
       <rPr>
@@ -25727,7 +25845,7 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">? </t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -25736,221 +25854,8 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>등</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끼니</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이름</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>뒤</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>조사를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문장에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>미리</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>써</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>두고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 32</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>자</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이내를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
       <t>지킴</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>{지난 끼니}을 드신 뒤 배부름은 어느 정도였나요?</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -26995,7 +26900,7 @@
         <v>2658</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="D22" s="12" t="s">
         <v>2659</v>
@@ -58429,7 +58334,7 @@
         <v>849</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>850</v>
@@ -60392,18 +60297,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -60425,18 +60330,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA5F7BAD-F7AB-4266-8370-535EF14A9159}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/files/diet-data-contract-v1.0.1.xlsx
+++ b/files/diet-data-contract-v1.0.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88D6B5C7-D1D2-4D2C-8D5E-88DA9FD01540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0C7934D-1326-44F3-B9C0-9A023F983539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8098" uniqueCount="2669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8090" uniqueCount="2662">
   <si>
     <t>항목</t>
   </si>
@@ -10977,254 +10977,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단백질</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질문</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>변경</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>지난</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끼니</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>고기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>생선</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>달걀</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>두부를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>드셨나요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>?</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질문</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> DIET-Q-06 · </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>참조설정데이터</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축정의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시트</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>단계</t>
     </r>
     <r>
@@ -24167,1144 +23919,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>질문</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문장</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>다듬기</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>{끼니</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>}</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>채소</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>반찬</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>몇</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>가지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>드셨나요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>? · {</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끼니</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">} </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>전후에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>음료</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>간식</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>몇</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>번</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>드셨나요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>? · {</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끼니</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">} </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>얼마나</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>배불렀나요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">? </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>등</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>질문</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시트</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> DIET-Q-01·02·03·05·06·07 · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>참조설정데이터</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축정의</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>야식</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질문을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>횟수에서</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>양으로</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>어젯밤</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>야식을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>몇</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>번</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>드셨나요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">? · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>안</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹었어요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>한</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>번</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>두</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>번</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이상</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>질문</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시트</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> DIET-Q-04 · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>선택지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시트</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 14~16</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>참조설정데이터</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축정의</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>어젯밤</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>야식은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>얼마나</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>드셨나요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">? · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>안</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹었어요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>간단히</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹었어요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>배부르게</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹었어요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>선택지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>코드는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> none · light · meal_sized, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>점수는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>그대로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>없음</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>배부르게 먹었어요</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -25322,7 +23936,89 @@
   </si>
   <si>
     <r>
-      <t>{끼니</t>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답변</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문장</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>다듬기</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>단백질</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
     </r>
     <r>
       <rPr>
@@ -25341,6 +24037,1139 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
+      <t>에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>고기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>생선</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>달걀</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두부를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>채소</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>채소</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>반찬</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>몇</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>음료</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>간식</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">} </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전후에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>음료</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>간식</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>몇</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>국물</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>국물은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>얼마나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>배부름</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>얼마나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>배불렀나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>야식</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>어젯밤</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>야식을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>몇</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">? </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>안</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹었어요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이상
+식사</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>거의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>못</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹거나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>거름</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>단백질</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
       <t>엔</t>
     </r>
     <r>
@@ -25360,6 +25189,140 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
+      <t>단백질류</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>고기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>생선</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>달걀</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>등</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
       <t>채소</t>
     </r>
     <r>
@@ -25370,6 +25333,63 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>엔</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>채소</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve"> </t>
     </r>
     <r>
@@ -25427,7 +25447,65 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t>? · {</t>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>음료</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>간식</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
     </r>
     <r>
       <rPr>
@@ -25560,7 +25638,27 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t>? · {</t>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>국물</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
     </r>
     <r>
       <rPr>
@@ -25579,6 +25677,121 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>엔</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>국물을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>얼마나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>배부름</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">} </t>
     </r>
     <r>
@@ -25636,6 +25849,102 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>야식</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>어젯밤</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>야식은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>얼마나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">? </t>
     </r>
     <r>
@@ -25645,26 +25954,332 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>등</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끼니</t>
+      <t>답</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>안</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹었어요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>간단히</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹었어요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>배부르게</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹었어요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>코드</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> none · light · meal_sized, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>점수</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없음</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그대로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식사</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>거의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>못</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹거나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>걸렀어요
+끼니</t>
     </r>
     <r>
       <rPr>
@@ -25807,6 +26422,44 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>치환</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>뒤</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve"> 32</t>
     </r>
     <r>
@@ -25835,26 +26488,146 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>이내를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>지킴</t>
+      <t>이하로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>맞춤</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DIET-Q-00~07 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>선택지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DIET-Q-00, DIET-Q-04 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>참조설정데이터</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축정의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
     </r>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -25974,7 +26747,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -26029,6 +26802,9 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -26713,7 +27489,7 @@
   <sheetPr>
     <tabColor rgb="FF315A7D"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1"/>
@@ -26864,60 +27640,32 @@
         <v>2533</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
-      <c r="A20" t="s">
-        <v>2534</v>
-      </c>
-      <c r="B20" t="s">
-        <v>2535</v>
-      </c>
-      <c r="C20" t="s">
-        <v>2652</v>
-      </c>
-      <c r="D20" t="s">
-        <v>2536</v>
+    <row r="20" spans="1:4" ht="140">
+      <c r="A20" s="20" t="s">
+        <v>2658</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>2659</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>2660</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>2661</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="12" t="s">
+        <v>2534</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>2535</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>2536</v>
+      </c>
+      <c r="D21" s="12" t="s">
         <v>2537</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>2538</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>2539</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>2540</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="12" t="s">
-        <v>2657</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>2658</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>2668</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>2659</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="12" t="s">
-        <v>2660</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>2661</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>2663</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>2662</v>
       </c>
     </row>
   </sheetData>
@@ -30945,13 +31693,13 @@
         <v>1439</v>
       </c>
       <c r="B66" t="s">
-        <v>2553</v>
+        <v>2550</v>
       </c>
       <c r="C66" t="s">
-        <v>2554</v>
+        <v>2551</v>
       </c>
       <c r="D66" t="s">
-        <v>2555</v>
+        <v>2552</v>
       </c>
       <c r="E66" t="s">
         <v>1421</v>
@@ -30960,7 +31708,7 @@
         <v>1205</v>
       </c>
       <c r="J66" t="s">
-        <v>2556</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="67" spans="1:10">
@@ -30968,13 +31716,13 @@
         <v>1441</v>
       </c>
       <c r="B67" t="s">
-        <v>2553</v>
+        <v>2550</v>
       </c>
       <c r="C67" t="s">
-        <v>2557</v>
+        <v>2554</v>
       </c>
       <c r="D67" t="s">
-        <v>2558</v>
+        <v>2555</v>
       </c>
       <c r="E67" t="s">
         <v>1421</v>
@@ -30983,7 +31731,7 @@
         <v>1205</v>
       </c>
       <c r="J67" t="s">
-        <v>2556</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -30994,10 +31742,10 @@
         <v>485</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>2560</v>
+        <v>2557</v>
       </c>
       <c r="E68" s="12" t="s">
         <v>1189</v>
@@ -31017,10 +31765,10 @@
         <v>485</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>2561</v>
+        <v>2558</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>2562</v>
+        <v>2559</v>
       </c>
       <c r="E69" s="12" t="s">
         <v>1189</v>
@@ -31615,7 +32363,7 @@
         <v>1500</v>
       </c>
       <c r="H24" t="s">
-        <v>2563</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -31635,7 +32383,7 @@
         <v>1500</v>
       </c>
       <c r="H25" t="s">
-        <v>2564</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -31655,7 +32403,7 @@
         <v>1505</v>
       </c>
       <c r="H26" t="s">
-        <v>2565</v>
+        <v>2562</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -31678,7 +32426,7 @@
         <v>1507</v>
       </c>
       <c r="H27" t="s">
-        <v>2566</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -31701,7 +32449,7 @@
         <v>1507</v>
       </c>
       <c r="H28" t="s">
-        <v>2567</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -31724,7 +32472,7 @@
         <v>1507</v>
       </c>
       <c r="H29" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -31747,7 +32495,7 @@
         <v>1507</v>
       </c>
       <c r="H30" t="s">
-        <v>2569</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -31770,7 +32518,7 @@
         <v>1507</v>
       </c>
       <c r="H31" t="s">
-        <v>2570</v>
+        <v>2567</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -31793,7 +32541,7 @@
         <v>1507</v>
       </c>
       <c r="H32" t="s">
-        <v>2571</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -31816,7 +32564,7 @@
         <v>1507</v>
       </c>
       <c r="H33" t="s">
-        <v>2572</v>
+        <v>2569</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -31839,7 +32587,7 @@
         <v>1507</v>
       </c>
       <c r="H34" t="s">
-        <v>2573</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -31862,7 +32610,7 @@
         <v>1500</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>2574</v>
+        <v>2571</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -31885,7 +32633,7 @@
         <v>1500</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>2575</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -31908,7 +32656,7 @@
         <v>1500</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>2576</v>
+        <v>2573</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -31931,7 +32679,7 @@
         <v>1500</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>2577</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -31954,7 +32702,7 @@
         <v>1500</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>2578</v>
+        <v>2575</v>
       </c>
     </row>
   </sheetData>
@@ -39122,13 +39870,13 @@
         <v>1958</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>2579</v>
+        <v>2576</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>2580</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -39167,10 +39915,10 @@
         <v>1968</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>2581</v>
+        <v>2578</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>2582</v>
+        <v>2579</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="28">
@@ -39276,13 +40024,13 @@
         <v>1997</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>2583</v>
+        <v>2580</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>2584</v>
+        <v>2581</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>2585</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -44934,7 +45682,7 @@
         <v>840</v>
       </c>
       <c r="C145" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D145" t="s">
         <v>2010</v>
@@ -44946,10 +45694,10 @@
         <v>1502</v>
       </c>
       <c r="G145" t="s">
-        <v>2587</v>
+        <v>2584</v>
       </c>
       <c r="H145" t="s">
-        <v>2588</v>
+        <v>2585</v>
       </c>
       <c r="I145" t="s">
         <v>964</v>
@@ -44958,7 +45706,7 @@
         <v>2463</v>
       </c>
       <c r="L145" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M145">
         <v>173</v>
@@ -44972,7 +45720,7 @@
         <v>840</v>
       </c>
       <c r="C146" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D146" t="s">
         <v>2010</v>
@@ -44984,16 +45732,16 @@
         <v>2023</v>
       </c>
       <c r="G146" t="s">
-        <v>2590</v>
+        <v>2587</v>
       </c>
       <c r="H146" t="s">
-        <v>2591</v>
+        <v>2588</v>
       </c>
       <c r="K146" t="s">
         <v>2465</v>
       </c>
       <c r="L146" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M146">
         <v>174</v>
@@ -45007,7 +45755,7 @@
         <v>840</v>
       </c>
       <c r="C147" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D147" t="s">
         <v>2010</v>
@@ -45019,16 +45767,16 @@
         <v>2023</v>
       </c>
       <c r="G147" t="s">
-        <v>2592</v>
+        <v>2589</v>
       </c>
       <c r="H147" t="s">
-        <v>2593</v>
+        <v>2590</v>
       </c>
       <c r="K147" t="s">
         <v>2467</v>
       </c>
       <c r="L147" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M147">
         <v>175</v>
@@ -45042,7 +45790,7 @@
         <v>840</v>
       </c>
       <c r="C148" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D148" t="s">
         <v>2010</v>
@@ -45054,16 +45802,16 @@
         <v>2023</v>
       </c>
       <c r="G148" t="s">
-        <v>2594</v>
+        <v>2591</v>
       </c>
       <c r="H148" t="s">
-        <v>2595</v>
+        <v>2592</v>
       </c>
       <c r="K148" t="s">
         <v>1541</v>
       </c>
       <c r="L148" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M148">
         <v>176</v>
@@ -45077,7 +45825,7 @@
         <v>840</v>
       </c>
       <c r="C149" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D149" t="s">
         <v>2010</v>
@@ -45089,16 +45837,16 @@
         <v>1502</v>
       </c>
       <c r="G149" t="s">
-        <v>2596</v>
+        <v>2593</v>
       </c>
       <c r="H149" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="K149" t="s">
         <v>2470</v>
       </c>
       <c r="L149" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M149">
         <v>177</v>
@@ -45112,7 +45860,7 @@
         <v>840</v>
       </c>
       <c r="C150" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D150" t="s">
         <v>2010</v>
@@ -45124,16 +45872,16 @@
         <v>1502</v>
       </c>
       <c r="G150" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="H150" t="s">
-        <v>2599</v>
+        <v>2596</v>
       </c>
       <c r="K150" t="s">
         <v>2472</v>
       </c>
       <c r="L150" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M150">
         <v>178</v>
@@ -45147,7 +45895,7 @@
         <v>840</v>
       </c>
       <c r="C151" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D151" t="s">
         <v>2010</v>
@@ -45159,16 +45907,16 @@
         <v>1502</v>
       </c>
       <c r="G151" t="s">
-        <v>2600</v>
+        <v>2597</v>
       </c>
       <c r="H151" t="s">
-        <v>2601</v>
+        <v>2598</v>
       </c>
       <c r="K151" t="s">
         <v>2472</v>
       </c>
       <c r="L151" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M151">
         <v>179</v>
@@ -45182,7 +45930,7 @@
         <v>840</v>
       </c>
       <c r="C152" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D152" t="s">
         <v>2010</v>
@@ -45194,16 +45942,16 @@
         <v>1502</v>
       </c>
       <c r="G152" t="s">
-        <v>2602</v>
+        <v>2599</v>
       </c>
       <c r="H152" t="s">
-        <v>2603</v>
+        <v>2600</v>
       </c>
       <c r="K152" t="s">
         <v>2475</v>
       </c>
       <c r="L152" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M152">
         <v>180</v>
@@ -45217,7 +45965,7 @@
         <v>840</v>
       </c>
       <c r="C153" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D153" t="s">
         <v>2010</v>
@@ -45229,16 +45977,16 @@
         <v>1502</v>
       </c>
       <c r="G153" t="s">
-        <v>2604</v>
+        <v>2601</v>
       </c>
       <c r="H153" t="s">
-        <v>2605</v>
+        <v>2602</v>
       </c>
       <c r="K153" t="s">
         <v>2477</v>
       </c>
       <c r="L153" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M153">
         <v>181</v>
@@ -45252,7 +46000,7 @@
         <v>840</v>
       </c>
       <c r="C154" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D154" t="s">
         <v>2010</v>
@@ -45264,16 +46012,16 @@
         <v>2011</v>
       </c>
       <c r="G154" t="s">
-        <v>2606</v>
+        <v>2603</v>
       </c>
       <c r="H154" t="s">
-        <v>2607</v>
+        <v>2604</v>
       </c>
       <c r="K154" t="s">
         <v>2465</v>
       </c>
       <c r="L154" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M154">
         <v>182</v>
@@ -45287,7 +46035,7 @@
         <v>840</v>
       </c>
       <c r="C155" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D155" t="s">
         <v>2010</v>
@@ -45299,16 +46047,16 @@
         <v>2011</v>
       </c>
       <c r="G155" t="s">
-        <v>2608</v>
+        <v>2605</v>
       </c>
       <c r="H155" t="s">
-        <v>2609</v>
+        <v>2606</v>
       </c>
       <c r="K155" t="s">
         <v>2463</v>
       </c>
       <c r="L155" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M155">
         <v>183</v>
@@ -45322,7 +46070,7 @@
         <v>840</v>
       </c>
       <c r="C156" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D156" t="s">
         <v>2010</v>
@@ -45334,16 +46082,16 @@
         <v>1502</v>
       </c>
       <c r="G156" t="s">
-        <v>2610</v>
+        <v>2607</v>
       </c>
       <c r="H156" t="s">
-        <v>2611</v>
+        <v>2608</v>
       </c>
       <c r="K156" t="s">
         <v>2465</v>
       </c>
       <c r="L156" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M156">
         <v>184</v>
@@ -45357,7 +46105,7 @@
         <v>840</v>
       </c>
       <c r="C157" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D157" t="s">
         <v>2010</v>
@@ -45369,10 +46117,10 @@
         <v>2023</v>
       </c>
       <c r="G157" t="s">
-        <v>2612</v>
+        <v>2609</v>
       </c>
       <c r="H157" t="s">
-        <v>2613</v>
+        <v>2610</v>
       </c>
       <c r="I157" t="s">
         <v>966</v>
@@ -45381,7 +46129,7 @@
         <v>2463</v>
       </c>
       <c r="L157" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M157">
         <v>185</v>
@@ -45395,7 +46143,7 @@
         <v>840</v>
       </c>
       <c r="C158" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D158" t="s">
         <v>2010</v>
@@ -45407,10 +46155,10 @@
         <v>1502</v>
       </c>
       <c r="G158" t="s">
-        <v>2614</v>
+        <v>2611</v>
       </c>
       <c r="H158" t="s">
-        <v>2615</v>
+        <v>2612</v>
       </c>
       <c r="I158" t="s">
         <v>964</v>
@@ -45419,7 +46167,7 @@
         <v>2463</v>
       </c>
       <c r="L158" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M158">
         <v>186</v>
@@ -45433,7 +46181,7 @@
         <v>840</v>
       </c>
       <c r="C159" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D159" t="s">
         <v>2010</v>
@@ -45445,16 +46193,16 @@
         <v>2023</v>
       </c>
       <c r="G159" t="s">
-        <v>2616</v>
+        <v>2613</v>
       </c>
       <c r="H159" t="s">
-        <v>2617</v>
+        <v>2614</v>
       </c>
       <c r="K159" t="s">
         <v>2470</v>
       </c>
       <c r="L159" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M159">
         <v>187</v>
@@ -45468,7 +46216,7 @@
         <v>840</v>
       </c>
       <c r="C160" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D160" t="s">
         <v>2010</v>
@@ -45480,16 +46228,16 @@
         <v>1502</v>
       </c>
       <c r="G160" t="s">
-        <v>2618</v>
+        <v>2615</v>
       </c>
       <c r="H160" t="s">
-        <v>2619</v>
+        <v>2616</v>
       </c>
       <c r="K160" t="s">
         <v>2485</v>
       </c>
       <c r="L160" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M160">
         <v>188</v>
@@ -45503,7 +46251,7 @@
         <v>840</v>
       </c>
       <c r="C161" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D161" t="s">
         <v>2010</v>
@@ -45515,16 +46263,16 @@
         <v>1502</v>
       </c>
       <c r="G161" t="s">
-        <v>2620</v>
+        <v>2617</v>
       </c>
       <c r="H161" t="s">
-        <v>2621</v>
+        <v>2618</v>
       </c>
       <c r="K161" t="s">
         <v>1541</v>
       </c>
       <c r="L161" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M161">
         <v>189</v>
@@ -45538,7 +46286,7 @@
         <v>840</v>
       </c>
       <c r="C162" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D162" t="s">
         <v>2010</v>
@@ -45550,16 +46298,16 @@
         <v>2023</v>
       </c>
       <c r="G162" t="s">
-        <v>2622</v>
+        <v>2619</v>
       </c>
       <c r="H162" t="s">
-        <v>2623</v>
+        <v>2620</v>
       </c>
       <c r="K162" t="s">
         <v>1541</v>
       </c>
       <c r="L162" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M162">
         <v>190</v>
@@ -45573,7 +46321,7 @@
         <v>840</v>
       </c>
       <c r="C163" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D163" t="s">
         <v>2010</v>
@@ -45585,16 +46333,16 @@
         <v>2011</v>
       </c>
       <c r="G163" t="s">
-        <v>2624</v>
+        <v>2621</v>
       </c>
       <c r="H163" t="s">
-        <v>2625</v>
+        <v>2622</v>
       </c>
       <c r="K163" t="s">
         <v>1541</v>
       </c>
       <c r="L163" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M163">
         <v>191</v>
@@ -45608,7 +46356,7 @@
         <v>840</v>
       </c>
       <c r="C164" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D164" t="s">
         <v>2010</v>
@@ -45620,16 +46368,16 @@
         <v>1502</v>
       </c>
       <c r="G164" t="s">
-        <v>2626</v>
+        <v>2623</v>
       </c>
       <c r="H164" t="s">
-        <v>2627</v>
+        <v>2624</v>
       </c>
       <c r="K164" t="s">
         <v>2014</v>
       </c>
       <c r="L164" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M164">
         <v>192</v>
@@ -45643,7 +46391,7 @@
         <v>840</v>
       </c>
       <c r="C165" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D165" t="s">
         <v>2010</v>
@@ -45655,16 +46403,16 @@
         <v>1502</v>
       </c>
       <c r="G165" t="s">
-        <v>2628</v>
+        <v>2625</v>
       </c>
       <c r="H165" t="s">
-        <v>2629</v>
+        <v>2626</v>
       </c>
       <c r="K165" t="s">
         <v>2472</v>
       </c>
       <c r="L165" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M165">
         <v>193</v>
@@ -45678,7 +46426,7 @@
         <v>840</v>
       </c>
       <c r="C166" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D166" t="s">
         <v>2010</v>
@@ -45690,16 +46438,16 @@
         <v>2011</v>
       </c>
       <c r="G166" t="s">
-        <v>2630</v>
+        <v>2627</v>
       </c>
       <c r="H166" t="s">
-        <v>2631</v>
+        <v>2628</v>
       </c>
       <c r="K166" t="s">
         <v>2472</v>
       </c>
       <c r="L166" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M166">
         <v>194</v>
@@ -45713,7 +46461,7 @@
         <v>840</v>
       </c>
       <c r="C167" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D167" t="s">
         <v>2010</v>
@@ -45725,16 +46473,16 @@
         <v>1502</v>
       </c>
       <c r="G167" t="s">
-        <v>2632</v>
+        <v>2629</v>
       </c>
       <c r="H167" t="s">
-        <v>2633</v>
+        <v>2630</v>
       </c>
       <c r="K167" t="s">
         <v>2477</v>
       </c>
       <c r="L167" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M167">
         <v>196</v>
@@ -45748,7 +46496,7 @@
         <v>840</v>
       </c>
       <c r="C168" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D168" t="s">
         <v>2010</v>
@@ -45760,16 +46508,16 @@
         <v>1502</v>
       </c>
       <c r="G168" t="s">
-        <v>2634</v>
+        <v>2631</v>
       </c>
       <c r="H168" t="s">
-        <v>2635</v>
+        <v>2632</v>
       </c>
       <c r="K168" t="s">
         <v>1541</v>
       </c>
       <c r="L168" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M168">
         <v>197</v>
@@ -45783,7 +46531,7 @@
         <v>840</v>
       </c>
       <c r="C169" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D169" t="s">
         <v>2010</v>
@@ -45795,16 +46543,16 @@
         <v>2011</v>
       </c>
       <c r="G169" t="s">
-        <v>2636</v>
+        <v>2633</v>
       </c>
       <c r="H169" t="s">
-        <v>2637</v>
+        <v>2634</v>
       </c>
       <c r="K169" t="s">
         <v>2463</v>
       </c>
       <c r="L169" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M169">
         <v>198</v>
@@ -45818,7 +46566,7 @@
         <v>840</v>
       </c>
       <c r="C170" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D170" t="s">
         <v>2010</v>
@@ -45830,16 +46578,16 @@
         <v>1502</v>
       </c>
       <c r="G170" t="s">
-        <v>2638</v>
+        <v>2635</v>
       </c>
       <c r="H170" t="s">
-        <v>2639</v>
+        <v>2636</v>
       </c>
       <c r="K170" t="s">
         <v>2465</v>
       </c>
       <c r="L170" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M170">
         <v>199</v>
@@ -45853,7 +46601,7 @@
         <v>840</v>
       </c>
       <c r="C171" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D171" t="s">
         <v>2010</v>
@@ -45865,10 +46613,10 @@
         <v>1502</v>
       </c>
       <c r="G171" t="s">
-        <v>2640</v>
+        <v>2637</v>
       </c>
       <c r="H171" t="s">
-        <v>2641</v>
+        <v>2638</v>
       </c>
       <c r="I171" t="s">
         <v>964</v>
@@ -45877,7 +46625,7 @@
         <v>2465</v>
       </c>
       <c r="L171" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M171">
         <v>200</v>
@@ -45891,7 +46639,7 @@
         <v>840</v>
       </c>
       <c r="C172" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D172" t="s">
         <v>2010</v>
@@ -45903,16 +46651,16 @@
         <v>2023</v>
       </c>
       <c r="G172" t="s">
-        <v>2642</v>
+        <v>2639</v>
       </c>
       <c r="H172" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="K172" t="s">
         <v>2014</v>
       </c>
       <c r="L172" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M172">
         <v>201</v>
@@ -45926,7 +46674,7 @@
         <v>840</v>
       </c>
       <c r="C173" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D173" t="s">
         <v>2010</v>
@@ -45938,16 +46686,16 @@
         <v>2011</v>
       </c>
       <c r="G173" t="s">
-        <v>2644</v>
+        <v>2641</v>
       </c>
       <c r="H173" t="s">
-        <v>2645</v>
+        <v>2642</v>
       </c>
       <c r="K173" t="s">
         <v>1541</v>
       </c>
       <c r="L173" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M173">
         <v>202</v>
@@ -50728,7 +51476,7 @@
         <v>840</v>
       </c>
       <c r="C156" t="s">
-        <v>2646</v>
+        <v>2643</v>
       </c>
       <c r="D156" t="s">
         <v>2515</v>
@@ -50757,7 +51505,7 @@
         <v>840</v>
       </c>
       <c r="C157" t="s">
-        <v>2646</v>
+        <v>2643</v>
       </c>
       <c r="D157" t="s">
         <v>2515</v>
@@ -51163,7 +51911,7 @@
         <v>840</v>
       </c>
       <c r="C171" t="s">
-        <v>2646</v>
+        <v>2643</v>
       </c>
       <c r="D171" t="s">
         <v>2515</v>
@@ -51786,7 +52534,7 @@
         <v>292</v>
       </c>
       <c r="I23" t="s">
-        <v>2541</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="24" customHeight="1">
@@ -53479,7 +54227,7 @@
         <v>449</v>
       </c>
       <c r="I100" t="s">
-        <v>2542</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="24" customHeight="1">
@@ -53984,7 +54732,7 @@
         <v>482</v>
       </c>
       <c r="I123" t="s">
-        <v>2543</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="24" customHeight="1">
@@ -54076,7 +54824,7 @@
         <v>292</v>
       </c>
       <c r="I127" t="s">
-        <v>2541</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="24" customHeight="1">
@@ -54377,7 +55125,7 @@
         <v>292</v>
       </c>
       <c r="I141" t="s">
-        <v>2544</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="24" customHeight="1">
@@ -54492,7 +55240,7 @@
         <v>518</v>
       </c>
       <c r="I146" t="s">
-        <v>2545</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="24" customHeight="1">
@@ -57962,7 +58710,7 @@
         <v>811</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>812</v>
@@ -57971,10 +58719,10 @@
         <v>813</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>2547</v>
+        <v>2544</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>2548</v>
+        <v>2545</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>427</v>
@@ -58100,19 +58848,19 @@
         <v>837</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>838</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>2550</v>
+        <v>2547</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>2551</v>
+        <v>2548</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>2552</v>
+        <v>2549</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>427</v>
@@ -58218,7 +58966,7 @@
         <v>849</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>2647</v>
+        <v>2644</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>850</v>
@@ -58247,7 +58995,7 @@
         <v>849</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>2648</v>
+        <v>2645</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>850</v>
@@ -58276,7 +59024,7 @@
         <v>849</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>2649</v>
+        <v>2646</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>850</v>
@@ -58305,16 +59053,16 @@
         <v>849</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>2650</v>
+        <v>2647</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>863</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>2665</v>
+        <v>2655</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>2651</v>
+        <v>2648</v>
       </c>
       <c r="I6" s="1">
         <v>6</v>
@@ -58334,7 +59082,7 @@
         <v>849</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>2667</v>
+        <v>2657</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>850</v>
@@ -58363,7 +59111,7 @@
         <v>849</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>2652</v>
+        <v>2649</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>850</v>
@@ -58392,7 +59140,7 @@
         <v>849</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>2653</v>
+        <v>2650</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>850</v>
@@ -58541,7 +59289,7 @@
         <v>887</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>2666</v>
+        <v>2656</v>
       </c>
       <c r="F4" s="1">
         <v>-1</v>
@@ -58789,10 +59537,10 @@
         <v>2</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>2654</v>
+        <v>2651</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>2655</v>
+        <v>2652</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1">
@@ -58810,10 +59558,10 @@
         <v>3</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>2656</v>
+        <v>2653</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>2664</v>
+        <v>2654</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1">
@@ -60297,18 +61045,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -60330,18 +61078,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA5F7BAD-F7AB-4266-8370-535EF14A9159}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/files/diet-data-contract-v1.0.1.xlsx
+++ b/files/diet-data-contract-v1.0.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01A67D2E-C255-4044-AD74-4EA092D00BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E35EC53-D6C4-4B8B-9B76-4BDA60A1BD0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24909,457 +24909,457 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
+    <t>{지난 끼니}엔 채소 반찬은 몇 가지였나요?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>{지난 끼니} 전후 단 음료·간식은 몇 번이었나요?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>{지난 끼니} 후 배부름은 어땠나요?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>거의 못 먹음</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>조금 먹었어요</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>7자 (5~7자)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>option_label은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>띄어쓰기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>포함</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 7</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>자</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이내</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(5~7</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>자</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>여야</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>버튼</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>폭이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>고정이라</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그보다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>길면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>버튼</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>높이가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>혼자</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>늘어난다</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>7자를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>넘는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>선택지를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적재하면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>거부</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>단백질: {끼니}엔 단백질류(고기·생선·달걀 등)를 드셨나요?
 채소: {끼니}엔 채소 반찬은 몇 가지였나요?
 단 음료·간식: {끼니} 전후 단 음료·간식은 몇 번이었나요?
 국물: {끼니}엔 국물을 얼마나 드셨나요?
 배부름: {끼니} 후 배부름은 어땠나요?
-야식: 어젯밤 야식은 얼마나 드셨나요? 답 안 먹었어요 · 조금 먹었어요 · 많이 먹었어요 (코드 none · light · meal_sized, 점수 없음 그대로)
+야식: 어젯밤 야식은 얼마나 드셨나요? 답 안 먹었어요 · 조금 먹었어요 · 배부르게 먹음 (코드 none · light · meal_sized, 점수 없음 그대로)
 식사 규칙 답: 거의 못 먹음
 끼니 이름 뒤 조사를 문장에 미리 써 두고, 치환 뒤 32자 이하로 맞춤</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>{지난 끼니}엔 채소 반찬은 몇 가지였나요?</t>
+    <t>전날 저녁 식사 후~당일 04:00 전의 야식 자기보고 양(조금 / 배부르게). 오늘 아침 식사는 제외. 위해성·수면 영향 판정 아님</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>{지난 끼니} 전후 단 음료·간식은 몇 번이었나요?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>전날 저녁 식사 후~당일 04:00 전의 야식 자기보고 양(조금 / 많이). 오늘 아침 식사는 제외. 위해성·수면 영향 판정 아님</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>{지난 끼니} 후 배부름은 어땠나요?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>거의 못 먹음</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>조금 먹었어요</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>많이 먹었어요</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>7자 (5~7자)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>option_label은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>띄어쓰기</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>포함</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 7</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>자</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이내</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>(5~7</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>자</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>여야</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>한다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>답</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>버튼</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>폭이</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>고정이라</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>그보다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>길면</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>버튼</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>높이가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>혼자</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>늘어난다</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>7자를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>넘는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>선택지를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>적재하면</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>거부</t>
-    </r>
+    <t>배부르게 먹음</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -26379,7 +26379,7 @@
         <v>2649</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>2651</v>
+        <v>2659</v>
       </c>
       <c r="D20" s="20" t="s">
         <v>2650</v>
@@ -29414,7 +29414,7 @@
         <v>1301</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>2659</v>
+        <v>2656</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>1189</v>
@@ -38744,10 +38744,10 @@
         <v>1993</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>2660</v>
+        <v>2657</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>2661</v>
+        <v>2658</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="28">
@@ -57697,7 +57697,7 @@
         <v>849</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>2652</v>
+        <v>2651</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>850</v>
@@ -57726,7 +57726,7 @@
         <v>849</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>2653</v>
+        <v>2652</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>850</v>
@@ -57790,7 +57790,7 @@
         <v>863</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>2654</v>
+        <v>2660</v>
       </c>
       <c r="H6" s="13" t="s">
         <v>2643</v>
@@ -57813,7 +57813,7 @@
         <v>849</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>2655</v>
+        <v>2653</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>850</v>
@@ -58020,7 +58020,7 @@
         <v>887</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>2656</v>
+        <v>2654</v>
       </c>
       <c r="F4" s="1">
         <v>-1</v>
@@ -58271,7 +58271,7 @@
         <v>2646</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>2657</v>
+        <v>2655</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1">
@@ -58292,7 +58292,7 @@
         <v>2647</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>2658</v>
+        <v>2661</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1">
@@ -59776,18 +59776,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -59809,18 +59809,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA5F7BAD-F7AB-4266-8370-535EF14A9159}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/files/diet-data-contract-v1.0.1.xlsx
+++ b/files/diet-data-contract-v1.0.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E35EC53-D6C4-4B8B-9B76-4BDA60A1BD0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B36ECD95-7E7F-4530-A8F5-5CE59F168781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8090" uniqueCount="2662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8090" uniqueCount="2663">
   <si>
     <t>항목</t>
   </si>
@@ -24922,10 +24922,6 @@
   </si>
   <si>
     <t>거의 못 먹음</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>조금 먹었어요</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -25349,17 +25345,25 @@
 단 음료·간식: {끼니} 전후 단 음료·간식은 몇 번이었나요?
 국물: {끼니}엔 국물을 얼마나 드셨나요?
 배부름: {끼니} 후 배부름은 어땠나요?
-야식: 어젯밤 야식은 얼마나 드셨나요? 답 안 먹었어요 · 조금 먹었어요 · 배부르게 먹음 (코드 none · light · meal_sized, 점수 없음 그대로)
+야식: 어젯밤 야식은 얼마나 드셨나요? 답 먹지 않음 · 조금 먹음 · 배불리 먹음 (코드 none · light · meal_sized, 점수 없음 그대로)
 식사 규칙 답: 거의 못 먹음
 끼니 이름 뒤 조사를 문장에 미리 써 두고, 치환 뒤 32자 이하로 맞춤</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>전날 저녁 식사 후~당일 04:00 전의 야식 자기보고 양(조금 / 배부르게). 오늘 아침 식사는 제외. 위해성·수면 영향 판정 아님</t>
+    <t>전날 저녁 식사 후~당일 04:00 전의 야식 자기보고 양(조금 / 배불리). 오늘 아침 식사는 제외. 위해성·수면 영향 판정 아님</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>배부르게 먹음</t>
+    <t>먹지 않음</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>조금 먹음</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>배불리 먹음</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -26379,7 +26383,7 @@
         <v>2649</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>2659</v>
+        <v>2658</v>
       </c>
       <c r="D20" s="20" t="s">
         <v>2650</v>
@@ -29414,7 +29418,7 @@
         <v>1301</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>2656</v>
+        <v>2655</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>1189</v>
@@ -38744,10 +38748,10 @@
         <v>1993</v>
       </c>
       <c r="C49" s="17" t="s">
+        <v>2656</v>
+      </c>
+      <c r="D49" s="17" t="s">
         <v>2657</v>
-      </c>
-      <c r="D49" s="17" t="s">
-        <v>2658</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="28">
@@ -57790,7 +57794,7 @@
         <v>863</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>2660</v>
+        <v>2659</v>
       </c>
       <c r="H6" s="13" t="s">
         <v>2643</v>
@@ -58249,8 +58253,8 @@
       <c r="D14" s="1" t="s">
         <v>892</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>899</v>
+      <c r="E14" s="13" t="s">
+        <v>2660</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1">
@@ -58271,7 +58275,7 @@
         <v>2646</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>2655</v>
+        <v>2661</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1">
@@ -58292,7 +58296,7 @@
         <v>2647</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>2661</v>
+        <v>2662</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1">
@@ -59776,18 +59780,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -59809,18 +59813,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA5F7BAD-F7AB-4266-8370-535EF14A9159}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/files/diet-data-contract-v1.0.1.xlsx
+++ b/files/diet-data-contract-v1.0.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA5FC95-D328-4A34-B38C-9E2CAA01AC62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C0C1ED4-E5C4-4AEF-A4E4-2993C381802B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -14233,106 +14233,6 @@
   </si>
   <si>
     <r>
-      <t>56일</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>그보다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>오래된</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>세지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않는다</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <rPr>
         <sz val="11"/>
         <rFont val="Carlito"/>
@@ -26851,32 +26751,342 @@
       </rPr>
       <t>행</t>
     </r>
+  </si>
+  <si>
+    <t>{지난 끼니}엔 채소 반찬을 얼마나 드셨나요?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>채소 반찬을 먹은 정도(본인 판단). 중량·먹는 순서 아님</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>본인이 느낀 양만 관찰. 400g 달성·혈당 개선으로 해석 금지</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>충분히 먹음</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>56일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그보다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>오래된</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>세지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않는다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정해진</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>근거</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>값이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아니며</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>앱</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>출시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>사용</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>데이터를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>보고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>조정한다</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>단백질: {끼니}엔 단백질류(고기·생선·달걀 등)를 드셨나요?
 채소: {끼니}엔 채소 반찬을 얼마나 드셨나요? 답 충분히 먹음 · 조금 먹음 · 먹지 않음
 단 음료·간식: {끼니} 전후 단 음료·간식은 몇 번이었나요?
-국물: {끼니}엔 국물을 얼마나 드셨나요?
+국물: {끼니}엔 국물을 얼마나 드셨나요? 답 먹지 않음 · 절반 이하 · 절반 넘게
 배부름: {끼니} 후 배부름은 어땠나요?
 야식: 어젯밤 야식은 얼마나 드셨나요? 답 먹지 않음 · 조금 먹음 · 배불리 먹음 (코드 none · light · meal_sized, 점수 없음 그대로)
 식사 규칙 답: 거의 못 먹음
 끼니 이름 뒤 조사를 문장에 미리 써 두고, 치환 뒤 32자 이하로 맞춤</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>{지난 끼니}엔 채소 반찬을 얼마나 드셨나요?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>채소 반찬을 먹은 정도(본인 판단). 중량·먹는 순서 아님</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>본인이 느낀 양만 관찰. 400g 달성·혈당 개선으로 해석 금지</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>충분히 먹음</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -27888,18 +28098,18 @@
         <v>2517</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="140">
+    <row r="20" spans="1:4" ht="154">
       <c r="A20" s="20" t="s">
+        <v>2634</v>
+      </c>
+      <c r="B20" s="20" t="s">
         <v>2635</v>
       </c>
-      <c r="B20" s="20" t="s">
+      <c r="C20" s="20" t="s">
+        <v>2664</v>
+      </c>
+      <c r="D20" s="20" t="s">
         <v>2636</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>2660</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>2637</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -27918,16 +28128,16 @@
     </row>
     <row r="22" spans="1:4" ht="56">
       <c r="A22" s="20" t="s">
+        <v>2655</v>
+      </c>
+      <c r="B22" s="20" t="s">
         <v>2656</v>
       </c>
-      <c r="B22" s="20" t="s">
+      <c r="C22" s="20" t="s">
         <v>2657</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="D22" s="20" t="s">
         <v>2658</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>2659</v>
       </c>
     </row>
   </sheetData>
@@ -30667,7 +30877,7 @@
         <v>1193</v>
       </c>
       <c r="J21" s="13" t="s">
-        <v>2655</v>
+        <v>2654</v>
       </c>
       <c r="K21" s="1">
         <v>21</v>
@@ -30945,7 +31155,7 @@
         <v>1288</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>2641</v>
+        <v>2640</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>1177</v>
@@ -32030,7 +32240,7 @@
         <v>2542</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>2543</v>
+        <v>2663</v>
       </c>
       <c r="E69" s="12" t="s">
         <v>1177</v>
@@ -32625,7 +32835,7 @@
         <v>1486</v>
       </c>
       <c r="H24" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -32645,7 +32855,7 @@
         <v>1486</v>
       </c>
       <c r="H25" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -32665,7 +32875,7 @@
         <v>1491</v>
       </c>
       <c r="H26" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -32688,7 +32898,7 @@
         <v>1493</v>
       </c>
       <c r="H27" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -32711,7 +32921,7 @@
         <v>1493</v>
       </c>
       <c r="H28" t="s">
-        <v>2548</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -32734,7 +32944,7 @@
         <v>1493</v>
       </c>
       <c r="H29" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -32757,7 +32967,7 @@
         <v>1493</v>
       </c>
       <c r="H30" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -32780,7 +32990,7 @@
         <v>1493</v>
       </c>
       <c r="H31" t="s">
-        <v>2551</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -32803,7 +33013,7 @@
         <v>1493</v>
       </c>
       <c r="H32" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -32826,7 +33036,7 @@
         <v>1493</v>
       </c>
       <c r="H33" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -32849,7 +33059,7 @@
         <v>1493</v>
       </c>
       <c r="H34" t="s">
-        <v>2554</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -32872,7 +33082,7 @@
         <v>1486</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -32895,7 +33105,7 @@
         <v>1486</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>2556</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -32918,7 +33128,7 @@
         <v>1486</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>2557</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -32941,7 +33151,7 @@
         <v>1486</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -32964,7 +33174,7 @@
         <v>1486</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>2559</v>
+        <v>2558</v>
       </c>
     </row>
   </sheetData>
@@ -40135,10 +40345,10 @@
         <v>2527</v>
       </c>
       <c r="C39" s="16" t="s">
+        <v>2559</v>
+      </c>
+      <c r="D39" s="16" t="s">
         <v>2560</v>
-      </c>
-      <c r="D39" s="16" t="s">
-        <v>2561</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -40177,10 +40387,10 @@
         <v>1954</v>
       </c>
       <c r="C42" s="17" t="s">
+        <v>2561</v>
+      </c>
+      <c r="D42" s="17" t="s">
         <v>2562</v>
-      </c>
-      <c r="D42" s="17" t="s">
-        <v>2563</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="28">
@@ -40275,10 +40485,10 @@
         <v>1980</v>
       </c>
       <c r="C49" s="17" t="s">
+        <v>2641</v>
+      </c>
+      <c r="D49" s="17" t="s">
         <v>2642</v>
-      </c>
-      <c r="D49" s="17" t="s">
-        <v>2643</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="28">
@@ -40286,13 +40496,13 @@
         <v>1981</v>
       </c>
       <c r="B50" s="16" t="s">
+        <v>2563</v>
+      </c>
+      <c r="C50" s="16" t="s">
         <v>2564</v>
       </c>
-      <c r="C50" s="16" t="s">
+      <c r="D50" s="16" t="s">
         <v>2565</v>
-      </c>
-      <c r="D50" s="16" t="s">
-        <v>2566</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -45944,7 +46154,7 @@
         <v>839</v>
       </c>
       <c r="C145" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D145" t="s">
         <v>1994</v>
@@ -45956,10 +46166,10 @@
         <v>1488</v>
       </c>
       <c r="G145" t="s">
+        <v>2567</v>
+      </c>
+      <c r="H145" t="s">
         <v>2568</v>
-      </c>
-      <c r="H145" t="s">
-        <v>2569</v>
       </c>
       <c r="I145" t="s">
         <v>952</v>
@@ -45968,7 +46178,7 @@
         <v>2447</v>
       </c>
       <c r="L145" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M145">
         <v>173</v>
@@ -45982,7 +46192,7 @@
         <v>839</v>
       </c>
       <c r="C146" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D146" t="s">
         <v>1994</v>
@@ -45994,16 +46204,16 @@
         <v>2007</v>
       </c>
       <c r="G146" t="s">
+        <v>2570</v>
+      </c>
+      <c r="H146" t="s">
         <v>2571</v>
-      </c>
-      <c r="H146" t="s">
-        <v>2572</v>
       </c>
       <c r="K146" t="s">
         <v>2449</v>
       </c>
       <c r="L146" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M146">
         <v>174</v>
@@ -46017,7 +46227,7 @@
         <v>839</v>
       </c>
       <c r="C147" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D147" t="s">
         <v>1994</v>
@@ -46029,16 +46239,16 @@
         <v>2007</v>
       </c>
       <c r="G147" t="s">
+        <v>2572</v>
+      </c>
+      <c r="H147" t="s">
         <v>2573</v>
-      </c>
-      <c r="H147" t="s">
-        <v>2574</v>
       </c>
       <c r="K147" t="s">
         <v>2451</v>
       </c>
       <c r="L147" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M147">
         <v>175</v>
@@ -46052,7 +46262,7 @@
         <v>839</v>
       </c>
       <c r="C148" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D148" t="s">
         <v>1994</v>
@@ -46064,16 +46274,16 @@
         <v>2007</v>
       </c>
       <c r="G148" t="s">
+        <v>2574</v>
+      </c>
+      <c r="H148" t="s">
         <v>2575</v>
-      </c>
-      <c r="H148" t="s">
-        <v>2576</v>
       </c>
       <c r="K148" t="s">
         <v>1527</v>
       </c>
       <c r="L148" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M148">
         <v>176</v>
@@ -46087,7 +46297,7 @@
         <v>839</v>
       </c>
       <c r="C149" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D149" t="s">
         <v>1994</v>
@@ -46099,16 +46309,16 @@
         <v>1488</v>
       </c>
       <c r="G149" t="s">
+        <v>2576</v>
+      </c>
+      <c r="H149" t="s">
         <v>2577</v>
-      </c>
-      <c r="H149" t="s">
-        <v>2578</v>
       </c>
       <c r="K149" t="s">
         <v>2454</v>
       </c>
       <c r="L149" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M149">
         <v>177</v>
@@ -46122,7 +46332,7 @@
         <v>839</v>
       </c>
       <c r="C150" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D150" t="s">
         <v>1994</v>
@@ -46134,16 +46344,16 @@
         <v>1488</v>
       </c>
       <c r="G150" t="s">
+        <v>2578</v>
+      </c>
+      <c r="H150" t="s">
         <v>2579</v>
-      </c>
-      <c r="H150" t="s">
-        <v>2580</v>
       </c>
       <c r="K150" t="s">
         <v>2456</v>
       </c>
       <c r="L150" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M150">
         <v>178</v>
@@ -46157,7 +46367,7 @@
         <v>839</v>
       </c>
       <c r="C151" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D151" t="s">
         <v>1994</v>
@@ -46169,16 +46379,16 @@
         <v>1488</v>
       </c>
       <c r="G151" t="s">
+        <v>2580</v>
+      </c>
+      <c r="H151" t="s">
         <v>2581</v>
-      </c>
-      <c r="H151" t="s">
-        <v>2582</v>
       </c>
       <c r="K151" t="s">
         <v>2456</v>
       </c>
       <c r="L151" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M151">
         <v>179</v>
@@ -46192,7 +46402,7 @@
         <v>839</v>
       </c>
       <c r="C152" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D152" t="s">
         <v>1994</v>
@@ -46204,16 +46414,16 @@
         <v>1488</v>
       </c>
       <c r="G152" t="s">
+        <v>2582</v>
+      </c>
+      <c r="H152" t="s">
         <v>2583</v>
-      </c>
-      <c r="H152" t="s">
-        <v>2584</v>
       </c>
       <c r="K152" t="s">
         <v>2459</v>
       </c>
       <c r="L152" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M152">
         <v>180</v>
@@ -46227,7 +46437,7 @@
         <v>839</v>
       </c>
       <c r="C153" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D153" t="s">
         <v>1994</v>
@@ -46239,16 +46449,16 @@
         <v>1488</v>
       </c>
       <c r="G153" t="s">
+        <v>2584</v>
+      </c>
+      <c r="H153" t="s">
         <v>2585</v>
-      </c>
-      <c r="H153" t="s">
-        <v>2586</v>
       </c>
       <c r="K153" t="s">
         <v>2461</v>
       </c>
       <c r="L153" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M153">
         <v>181</v>
@@ -46262,7 +46472,7 @@
         <v>839</v>
       </c>
       <c r="C154" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D154" t="s">
         <v>1994</v>
@@ -46274,16 +46484,16 @@
         <v>1995</v>
       </c>
       <c r="G154" t="s">
+        <v>2586</v>
+      </c>
+      <c r="H154" t="s">
         <v>2587</v>
-      </c>
-      <c r="H154" t="s">
-        <v>2588</v>
       </c>
       <c r="K154" t="s">
         <v>2449</v>
       </c>
       <c r="L154" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M154">
         <v>182</v>
@@ -46297,7 +46507,7 @@
         <v>839</v>
       </c>
       <c r="C155" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D155" t="s">
         <v>1994</v>
@@ -46309,16 +46519,16 @@
         <v>1995</v>
       </c>
       <c r="G155" t="s">
+        <v>2588</v>
+      </c>
+      <c r="H155" t="s">
         <v>2589</v>
-      </c>
-      <c r="H155" t="s">
-        <v>2590</v>
       </c>
       <c r="K155" t="s">
         <v>2447</v>
       </c>
       <c r="L155" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M155">
         <v>183</v>
@@ -46332,7 +46542,7 @@
         <v>839</v>
       </c>
       <c r="C156" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D156" t="s">
         <v>1994</v>
@@ -46344,16 +46554,16 @@
         <v>1488</v>
       </c>
       <c r="G156" t="s">
+        <v>2590</v>
+      </c>
+      <c r="H156" t="s">
         <v>2591</v>
-      </c>
-      <c r="H156" t="s">
-        <v>2592</v>
       </c>
       <c r="K156" t="s">
         <v>2449</v>
       </c>
       <c r="L156" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M156">
         <v>184</v>
@@ -46367,7 +46577,7 @@
         <v>839</v>
       </c>
       <c r="C157" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D157" t="s">
         <v>1994</v>
@@ -46379,10 +46589,10 @@
         <v>2007</v>
       </c>
       <c r="G157" t="s">
+        <v>2592</v>
+      </c>
+      <c r="H157" t="s">
         <v>2593</v>
-      </c>
-      <c r="H157" t="s">
-        <v>2594</v>
       </c>
       <c r="I157" t="s">
         <v>954</v>
@@ -46391,7 +46601,7 @@
         <v>2447</v>
       </c>
       <c r="L157" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M157">
         <v>185</v>
@@ -46405,7 +46615,7 @@
         <v>839</v>
       </c>
       <c r="C158" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D158" t="s">
         <v>1994</v>
@@ -46417,10 +46627,10 @@
         <v>1488</v>
       </c>
       <c r="G158" t="s">
+        <v>2594</v>
+      </c>
+      <c r="H158" t="s">
         <v>2595</v>
-      </c>
-      <c r="H158" t="s">
-        <v>2596</v>
       </c>
       <c r="I158" t="s">
         <v>952</v>
@@ -46429,7 +46639,7 @@
         <v>2447</v>
       </c>
       <c r="L158" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M158">
         <v>186</v>
@@ -46443,7 +46653,7 @@
         <v>839</v>
       </c>
       <c r="C159" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D159" t="s">
         <v>1994</v>
@@ -46455,16 +46665,16 @@
         <v>2007</v>
       </c>
       <c r="G159" t="s">
+        <v>2596</v>
+      </c>
+      <c r="H159" t="s">
         <v>2597</v>
-      </c>
-      <c r="H159" t="s">
-        <v>2598</v>
       </c>
       <c r="K159" t="s">
         <v>2454</v>
       </c>
       <c r="L159" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M159">
         <v>187</v>
@@ -46478,7 +46688,7 @@
         <v>839</v>
       </c>
       <c r="C160" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D160" t="s">
         <v>1994</v>
@@ -46490,16 +46700,16 @@
         <v>1488</v>
       </c>
       <c r="G160" t="s">
+        <v>2598</v>
+      </c>
+      <c r="H160" t="s">
         <v>2599</v>
-      </c>
-      <c r="H160" t="s">
-        <v>2600</v>
       </c>
       <c r="K160" t="s">
         <v>2469</v>
       </c>
       <c r="L160" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M160">
         <v>188</v>
@@ -46513,7 +46723,7 @@
         <v>839</v>
       </c>
       <c r="C161" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D161" t="s">
         <v>1994</v>
@@ -46525,16 +46735,16 @@
         <v>1488</v>
       </c>
       <c r="G161" t="s">
+        <v>2600</v>
+      </c>
+      <c r="H161" t="s">
         <v>2601</v>
-      </c>
-      <c r="H161" t="s">
-        <v>2602</v>
       </c>
       <c r="K161" t="s">
         <v>1527</v>
       </c>
       <c r="L161" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M161">
         <v>189</v>
@@ -46548,7 +46758,7 @@
         <v>839</v>
       </c>
       <c r="C162" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D162" t="s">
         <v>1994</v>
@@ -46560,16 +46770,16 @@
         <v>2007</v>
       </c>
       <c r="G162" t="s">
+        <v>2602</v>
+      </c>
+      <c r="H162" t="s">
         <v>2603</v>
-      </c>
-      <c r="H162" t="s">
-        <v>2604</v>
       </c>
       <c r="K162" t="s">
         <v>1527</v>
       </c>
       <c r="L162" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M162">
         <v>190</v>
@@ -46583,7 +46793,7 @@
         <v>839</v>
       </c>
       <c r="C163" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D163" t="s">
         <v>1994</v>
@@ -46595,16 +46805,16 @@
         <v>1995</v>
       </c>
       <c r="G163" t="s">
+        <v>2604</v>
+      </c>
+      <c r="H163" t="s">
         <v>2605</v>
-      </c>
-      <c r="H163" t="s">
-        <v>2606</v>
       </c>
       <c r="K163" t="s">
         <v>1527</v>
       </c>
       <c r="L163" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M163">
         <v>191</v>
@@ -46618,7 +46828,7 @@
         <v>839</v>
       </c>
       <c r="C164" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D164" t="s">
         <v>1994</v>
@@ -46630,16 +46840,16 @@
         <v>1488</v>
       </c>
       <c r="G164" t="s">
+        <v>2606</v>
+      </c>
+      <c r="H164" t="s">
         <v>2607</v>
-      </c>
-      <c r="H164" t="s">
-        <v>2608</v>
       </c>
       <c r="K164" t="s">
         <v>1998</v>
       </c>
       <c r="L164" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M164">
         <v>192</v>
@@ -46653,7 +46863,7 @@
         <v>839</v>
       </c>
       <c r="C165" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D165" t="s">
         <v>1994</v>
@@ -46665,16 +46875,16 @@
         <v>1488</v>
       </c>
       <c r="G165" t="s">
+        <v>2608</v>
+      </c>
+      <c r="H165" t="s">
         <v>2609</v>
-      </c>
-      <c r="H165" t="s">
-        <v>2610</v>
       </c>
       <c r="K165" t="s">
         <v>2456</v>
       </c>
       <c r="L165" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M165">
         <v>193</v>
@@ -46688,7 +46898,7 @@
         <v>839</v>
       </c>
       <c r="C166" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D166" t="s">
         <v>1994</v>
@@ -46700,16 +46910,16 @@
         <v>1995</v>
       </c>
       <c r="G166" t="s">
+        <v>2610</v>
+      </c>
+      <c r="H166" t="s">
         <v>2611</v>
-      </c>
-      <c r="H166" t="s">
-        <v>2612</v>
       </c>
       <c r="K166" t="s">
         <v>2456</v>
       </c>
       <c r="L166" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M166">
         <v>194</v>
@@ -46723,7 +46933,7 @@
         <v>839</v>
       </c>
       <c r="C167" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D167" t="s">
         <v>1994</v>
@@ -46735,16 +46945,16 @@
         <v>1488</v>
       </c>
       <c r="G167" t="s">
+        <v>2612</v>
+      </c>
+      <c r="H167" t="s">
         <v>2613</v>
-      </c>
-      <c r="H167" t="s">
-        <v>2614</v>
       </c>
       <c r="K167" t="s">
         <v>2461</v>
       </c>
       <c r="L167" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M167">
         <v>196</v>
@@ -46758,7 +46968,7 @@
         <v>839</v>
       </c>
       <c r="C168" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D168" t="s">
         <v>1994</v>
@@ -46770,16 +46980,16 @@
         <v>1488</v>
       </c>
       <c r="G168" t="s">
+        <v>2614</v>
+      </c>
+      <c r="H168" t="s">
         <v>2615</v>
-      </c>
-      <c r="H168" t="s">
-        <v>2616</v>
       </c>
       <c r="K168" t="s">
         <v>1527</v>
       </c>
       <c r="L168" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M168">
         <v>197</v>
@@ -46793,7 +47003,7 @@
         <v>839</v>
       </c>
       <c r="C169" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D169" t="s">
         <v>1994</v>
@@ -46805,16 +47015,16 @@
         <v>1995</v>
       </c>
       <c r="G169" t="s">
+        <v>2616</v>
+      </c>
+      <c r="H169" t="s">
         <v>2617</v>
-      </c>
-      <c r="H169" t="s">
-        <v>2618</v>
       </c>
       <c r="K169" t="s">
         <v>2447</v>
       </c>
       <c r="L169" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M169">
         <v>198</v>
@@ -46828,7 +47038,7 @@
         <v>839</v>
       </c>
       <c r="C170" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D170" t="s">
         <v>1994</v>
@@ -46840,16 +47050,16 @@
         <v>1488</v>
       </c>
       <c r="G170" t="s">
+        <v>2618</v>
+      </c>
+      <c r="H170" t="s">
         <v>2619</v>
-      </c>
-      <c r="H170" t="s">
-        <v>2620</v>
       </c>
       <c r="K170" t="s">
         <v>2449</v>
       </c>
       <c r="L170" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M170">
         <v>199</v>
@@ -46863,7 +47073,7 @@
         <v>839</v>
       </c>
       <c r="C171" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D171" t="s">
         <v>1994</v>
@@ -46875,10 +47085,10 @@
         <v>1488</v>
       </c>
       <c r="G171" t="s">
+        <v>2620</v>
+      </c>
+      <c r="H171" t="s">
         <v>2621</v>
-      </c>
-      <c r="H171" t="s">
-        <v>2622</v>
       </c>
       <c r="I171" t="s">
         <v>952</v>
@@ -46887,7 +47097,7 @@
         <v>2449</v>
       </c>
       <c r="L171" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M171">
         <v>200</v>
@@ -46901,7 +47111,7 @@
         <v>839</v>
       </c>
       <c r="C172" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D172" t="s">
         <v>1994</v>
@@ -46913,16 +47123,16 @@
         <v>2007</v>
       </c>
       <c r="G172" t="s">
+        <v>2622</v>
+      </c>
+      <c r="H172" t="s">
         <v>2623</v>
-      </c>
-      <c r="H172" t="s">
-        <v>2624</v>
       </c>
       <c r="K172" t="s">
         <v>1998</v>
       </c>
       <c r="L172" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M172">
         <v>201</v>
@@ -46936,7 +47146,7 @@
         <v>839</v>
       </c>
       <c r="C173" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D173" t="s">
         <v>1994</v>
@@ -46948,16 +47158,16 @@
         <v>1995</v>
       </c>
       <c r="G173" t="s">
+        <v>2624</v>
+      </c>
+      <c r="H173" t="s">
         <v>2625</v>
-      </c>
-      <c r="H173" t="s">
-        <v>2626</v>
       </c>
       <c r="K173" t="s">
         <v>1527</v>
       </c>
       <c r="L173" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M173">
         <v>202</v>
@@ -51738,7 +51948,7 @@
         <v>839</v>
       </c>
       <c r="C156" t="s">
-        <v>2627</v>
+        <v>2626</v>
       </c>
       <c r="D156" t="s">
         <v>2499</v>
@@ -51767,7 +51977,7 @@
         <v>839</v>
       </c>
       <c r="C157" t="s">
-        <v>2627</v>
+        <v>2626</v>
       </c>
       <c r="D157" t="s">
         <v>2499</v>
@@ -52173,7 +52383,7 @@
         <v>839</v>
       </c>
       <c r="C171" t="s">
-        <v>2627</v>
+        <v>2626</v>
       </c>
       <c r="D171" t="s">
         <v>2499</v>
@@ -58935,7 +59145,7 @@
         <v>802</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>2648</v>
+        <v>2647</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>803</v>
@@ -59202,7 +59412,7 @@
         <v>842</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>2649</v>
+        <v>2648</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>843</v>
@@ -59228,16 +59438,16 @@
         <v>847</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>2661</v>
+        <v>2659</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>848</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>2662</v>
+        <v>2660</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>2663</v>
+        <v>2661</v>
       </c>
       <c r="I3" s="1">
         <v>3</v>
@@ -59257,7 +59467,7 @@
         <v>847</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>2638</v>
+        <v>2637</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>848</v>
@@ -59286,7 +59496,7 @@
         <v>847</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>2628</v>
+        <v>2627</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>848</v>
@@ -59315,16 +59525,16 @@
         <v>847</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>2629</v>
+        <v>2628</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>859</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>2644</v>
+        <v>2643</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>2630</v>
+        <v>2629</v>
       </c>
       <c r="I6" s="1">
         <v>6</v>
@@ -59344,7 +59554,7 @@
         <v>847</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>2639</v>
+        <v>2638</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>848</v>
@@ -59373,7 +59583,7 @@
         <v>847</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>2631</v>
+        <v>2630</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>848</v>
@@ -59402,7 +59612,7 @@
         <v>847</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>2632</v>
+        <v>2631</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>848</v>
@@ -59431,16 +59641,16 @@
         <v>874</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>2650</v>
+        <v>2649</v>
       </c>
       <c r="F10" t="s">
         <v>875</v>
       </c>
       <c r="G10" s="12" t="s">
+        <v>2650</v>
+      </c>
+      <c r="H10" s="12" t="s">
         <v>2651</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>2652</v>
       </c>
     </row>
   </sheetData>
@@ -59551,7 +59761,7 @@
         <v>880</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>2640</v>
+        <v>2639</v>
       </c>
       <c r="F4" s="1">
         <v>-1</v>
@@ -59574,7 +59784,7 @@
         <v>881</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>2664</v>
+        <v>2662</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
@@ -59597,7 +59807,7 @@
         <v>882</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>2646</v>
+        <v>2645</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -59620,7 +59830,7 @@
         <v>883</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>2645</v>
+        <v>2644</v>
       </c>
       <c r="F7" s="1">
         <v>-1</v>
@@ -59711,8 +59921,8 @@
       <c r="D11" s="1" t="s">
         <v>883</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>889</v>
+      <c r="E11" s="13" t="s">
+        <v>2644</v>
       </c>
       <c r="F11" s="1">
         <v>1</v>
@@ -59781,7 +59991,7 @@
         <v>883</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>2645</v>
+        <v>2644</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1">
@@ -59799,10 +60009,10 @@
         <v>2</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>2633</v>
+        <v>2632</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>2646</v>
+        <v>2645</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1">
@@ -59820,10 +60030,10 @@
         <v>3</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>2634</v>
+        <v>2633</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>2647</v>
+        <v>2646</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1">
@@ -60051,7 +60261,7 @@
         <v>905</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>2653</v>
+        <v>2652</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -60085,7 +60295,7 @@
         <v>908</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>2654</v>
+        <v>2653</v>
       </c>
     </row>
   </sheetData>
@@ -61307,18 +61517,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -61340,18 +61550,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA5F7BAD-F7AB-4266-8370-535EF14A9159}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/files/diet-data-contract-v1.0.1.xlsx
+++ b/files/diet-data-contract-v1.0.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED1096B-27FC-4BA8-9DB2-400C9AD2B375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A41202F-5DD0-493D-BDA6-41618649F4BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8102" uniqueCount="2673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8106" uniqueCount="2684">
   <si>
     <t>항목</t>
   </si>
@@ -29176,6 +29176,1953 @@
         <rFont val="Carlito"/>
       </rPr>
       <t>선택</t>
+    </r>
+  </si>
+  <si>
+    <t>DIET-Q-04</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>INTRO</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>보류</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>근거 범위에 맞춰 이유 문장 수정. 10-07 보류: 끼니 규칙 축은 목표 축이 되지 않아 나올 수 없고 「주말도 아침 챙기기」와 겹침</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>근거 범위에 맞춰 이유 문장 수정. 10-07 보류: 식사 시각 질문은 아침에만 묻고 이 문구는 저녁 전용·식후 불가라 나올 수 없음. 식후 가능으로 바꿀지 정한 뒤 되살린다</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>WEEKEND</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>토</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>일</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>요일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>조건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정리</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>출근길에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>평일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">): </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>도전</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>→</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>될</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없어</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>안</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>나옴
+주말에도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>주말</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">): </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이유로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>안</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>나옴
+주말도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식사</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시각</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>입문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">): </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>요일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>조건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없음</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>→</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>월요일에도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>나옴
+주말</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>저녁도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>제때</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식사</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시각</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>기본</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">): </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>저녁</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전용이고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>불가라</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>안</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>나옴</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>출근길에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식사</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시각</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>입문으로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>옮김</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>평일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>조건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그대로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>주말에도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>보류</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>주말도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기와</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>겹침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>주말도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>노출조건에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>주말</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>토</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>추가
+주말</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>저녁도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>제때</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>보류</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식사</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시각</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침에만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묻고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>저녁</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>되지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않음</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>목표문구</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DIET-P-0088 E·F</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>열</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, DIET-P-0043·0157 source_status · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>노출조건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DIET-P-0264 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>참조설정데이터</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구세트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
     </r>
   </si>
 </sst>
@@ -29294,7 +31241,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -29352,6 +31299,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -30036,7 +31986,7 @@
   <sheetPr>
     <tabColor rgb="FF315A7D"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1"/>
@@ -30241,6 +32191,20 @@
       </c>
       <c r="D23" s="20" t="s">
         <v>2672</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="98">
+      <c r="A24" s="20" t="s">
+        <v>2680</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>2681</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>2682</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>2683</v>
       </c>
     </row>
   </sheetData>
@@ -44147,8 +46111,8 @@
       <c r="B36" s="8" t="s">
         <v>838</v>
       </c>
-      <c r="C36" s="8" t="s">
-        <v>1990</v>
+      <c r="C36" s="21" t="s">
+        <v>2675</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>1991</v>
@@ -44172,8 +46136,8 @@
       <c r="K36" s="8" t="s">
         <v>1995</v>
       </c>
-      <c r="L36" s="8" t="s">
-        <v>1996</v>
+      <c r="L36" s="21" t="s">
+        <v>2676</v>
       </c>
       <c r="M36" s="8">
         <v>36</v>
@@ -45295,11 +47259,11 @@
       <c r="D66" s="8" t="s">
         <v>1991</v>
       </c>
-      <c r="E66" s="8" t="s">
-        <v>837</v>
-      </c>
-      <c r="F66" s="8" t="s">
-        <v>2004</v>
+      <c r="E66" s="21" t="s">
+        <v>2673</v>
+      </c>
+      <c r="F66" s="21" t="s">
+        <v>2674</v>
       </c>
       <c r="G66" s="11" t="s">
         <v>2199</v>
@@ -46513,8 +48477,8 @@
       <c r="B98" s="8" t="s">
         <v>838</v>
       </c>
-      <c r="C98" s="8" t="s">
-        <v>1990</v>
+      <c r="C98" s="21" t="s">
+        <v>2675</v>
       </c>
       <c r="D98" s="8" t="s">
         <v>1991</v>
@@ -46536,8 +48500,8 @@
       <c r="K98" s="8" t="s">
         <v>2051</v>
       </c>
-      <c r="L98" s="8" t="s">
-        <v>1996</v>
+      <c r="L98" s="21" t="s">
+        <v>2677</v>
       </c>
       <c r="M98" s="8">
         <v>123</v>
@@ -54441,14 +56405,14 @@
       <c r="B169" t="s">
         <v>838</v>
       </c>
-      <c r="C169" t="s">
-        <v>2486</v>
+      <c r="C169" s="12" t="s">
+        <v>2679</v>
       </c>
       <c r="D169" t="s">
         <v>326</v>
       </c>
-      <c r="E169" t="s">
-        <v>326</v>
+      <c r="E169" s="12" t="s">
+        <v>2678</v>
       </c>
       <c r="F169" t="s">
         <v>326</v>
@@ -63634,18 +65598,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -63667,18 +65631,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA5F7BAD-F7AB-4266-8370-535EF14A9159}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/files/diet-data-contract-v1.0.1.xlsx
+++ b/files/diet-data-contract-v1.0.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A41202F-5DD0-493D-BDA6-41618649F4BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{486D83BE-DC1F-4D17-A145-17307EF39B54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8106" uniqueCount="2684">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8162" uniqueCount="2703">
   <si>
     <t>항목</t>
   </si>
@@ -9737,10 +9737,6 @@
   </si>
   <si>
     <t>PRE_MIDNIGHT</t>
-  </si>
-  <si>
-    <t>질문 9, 선택지 27, 목표문구 172, 노출조건 172, 질환규칙 14, 상병코드조건 61, 설정 68</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>동일 축의 축 목표가 완료되지 않은 채 끝난 것 연속 2건</t>
@@ -24422,383 +24418,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>17~24시와</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 00~04</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>식후</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> READY</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이면서</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> after_dinner_eligible=true</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>인</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 13</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>후보로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>사용한다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>. 17~24</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 13</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>, 00~04</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>저녁</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>전체</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시간대</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>(EVENING)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>맞는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 2</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>사용한다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>마지막 단계 변경 이후 그 축의 확정된 축 목표 최근 4건 중 3건 완료. 확정된 축 목표가 3건 미만이면 판단하지 않음</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -31123,6 +30742,3801 @@
         <rFont val="Carlito"/>
       </rPr>
       <t>시트</t>
+    </r>
+  </si>
+  <si>
+    <t>DIET-P-0269</t>
+  </si>
+  <si>
+    <r>
+      <t>출출하면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가볍게</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>요기하기</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>저녁을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적게</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹어</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>허기가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>지면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>소화가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>편한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>음식을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>조금</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹어요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>10-07 추가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>저녁</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표용</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가능</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>자정</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전</t>
+    </r>
+  </si>
+  <si>
+    <t>DIET-P-0270</t>
+  </si>
+  <si>
+    <r>
+      <t>따뜻한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>우유나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두유</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>잔</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>따뜻한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>음료로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>속을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>달래며</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>부족한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>조금</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>채워요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전체를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대신하지는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않아요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>DIET-P-0271</t>
+  </si>
+  <si>
+    <r>
+      <t>내일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙길</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>것</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>준비하기</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>저녁을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적게</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>날은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>내일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침거리를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>미리</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>준비해</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>둬요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>17~24시와</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 00~04</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> READY</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이면서</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> after_dinner_eligible=true</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>인</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 17</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>후보로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>사용한다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>. 17~24</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 17</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>, 00~04</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>저녁</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전체</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시간대</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(EVENING)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>맞는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>사용한다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>질문 9, 선택지 27, 목표문구 175, 노출조건 175, 질환규칙 14, 상병코드조건 61, 설정 68</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>V-52</t>
+  </si>
+  <si>
+    <r>
+      <t>저녁</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>우선</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>17시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이후에도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>고정</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>「조금</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적게」「거의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>못</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹거나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>걸렀어요」이면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>풀을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먼저</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>쓴다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이때는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가능</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(after_dinner_eligible=true)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>인</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>후보로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>하고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그날</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질환</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>금지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>성격</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시간</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>달력</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>조건을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>다시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적용한다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>후보가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>하나도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>남지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않으면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>넘어간다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>저녁에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대상</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>했는데</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가능</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>있는데도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>나오지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않으면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>거부</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>저녁</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>추가</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>저녁</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(17</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>에는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가능</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>쓰는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>때문에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 0</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개라</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>「조금</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적게」「거의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>못</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹거나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>걸렀어요」를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답해도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>나오지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않음</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>다음</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가능으로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>바꾸고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>자정</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>추가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>출출하면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가볍게</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>요기하기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>따뜻한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>우유나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두유</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>잔</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>내일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙길</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>것</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>준비하기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>저녁에도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먼저</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>쓰고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번갈아</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>나옴</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>후보</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 13</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>→</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 17</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(17~24</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 17</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>, 00~04</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>목표문구</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>노출조건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DIET-P-0033, 0269~0271 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>구현기준</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> R-05 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>검증규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> V-52 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>참조설정데이터</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구세트</t>
     </r>
   </si>
 </sst>
@@ -31241,7 +34655,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -31302,6 +34716,14 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -31611,7 +35033,7 @@
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{00000000-000C-0000-FFFF-FFFF16000000}" name="DietValidationRules" displayName="DietValidationRules" ref="A1:D51" totalsRowShown="0" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{00000000-000C-0000-FFFF-FFFF16000000}" name="DietValidationRules" displayName="DietValidationRules" ref="A1:D52" totalsRowShown="0" dataDxfId="4">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-1600-000001000000}" name="규칙 ID" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-1600-000002000000}" name="대상" dataDxfId="2"/>
@@ -31637,7 +35059,7 @@
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="58" xr:uid="{00000000-000C-0000-FFFF-FFFF18000000}" name="DietGoalPhrasesClean" displayName="DietGoalPhrasesClean" ref="A1:M173" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="58" xr:uid="{00000000-000C-0000-FFFF-FFFF18000000}" name="DietGoalPhrasesClean" displayName="DietGoalPhrasesClean" ref="A1:M176" totalsRowShown="0">
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-1800-000001000000}" name="phrase_id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-1800-000002000000}" name="phrase_version"/>
@@ -31658,8 +35080,8 @@
 </file>
 
 <file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="59" xr:uid="{00000000-000C-0000-FFFF-FFFF19000000}" name="DietPhraseApplicabilityClean" displayName="DietPhraseApplicabilityClean" ref="A1:K173" totalsRowShown="0">
-  <autoFilter ref="A1:K173" xr:uid="{00000000-000C-0000-FFFF-FFFF19000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="59" xr:uid="{00000000-000C-0000-FFFF-FFFF19000000}" name="DietPhraseApplicabilityClean" displayName="DietPhraseApplicabilityClean" ref="A1:K176" totalsRowShown="0">
+  <autoFilter ref="A1:K176" xr:uid="{00000000-000C-0000-FFFF-FFFF19000000}">
     <filterColumn colId="6">
       <filters>
         <filter val="TRUE"/>
@@ -31986,7 +35408,7 @@
   <sheetPr>
     <tabColor rgb="FF315A7D"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1"/>
@@ -32003,10 +35425,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>2505</v>
+      </c>
+      <c r="D1" t="s">
         <v>2506</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2507</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="24" customHeight="1">
@@ -32078,7 +35500,7 @@
         <v>18</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>2497</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="24" customHeight="1">
@@ -32115,96 +35537,110 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>2508</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>2509</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
+        <v>2509</v>
+      </c>
+      <c r="B19" t="s">
         <v>2510</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>2511</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>2512</v>
-      </c>
-      <c r="D19" t="s">
-        <v>2513</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="154">
       <c r="A20" s="20" t="s">
+        <v>2622</v>
+      </c>
+      <c r="B20" s="20" t="s">
         <v>2623</v>
       </c>
-      <c r="B20" s="20" t="s">
+      <c r="C20" s="20" t="s">
+        <v>2652</v>
+      </c>
+      <c r="D20" s="20" t="s">
         <v>2624</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>2653</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>2625</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="12" t="s">
+        <v>2513</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>2514</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="C21" s="12" t="s">
+        <v>2653</v>
+      </c>
+      <c r="D21" s="12" t="s">
         <v>2515</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>2654</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>2516</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="56">
       <c r="A22" s="20" t="s">
+        <v>2643</v>
+      </c>
+      <c r="B22" s="20" t="s">
         <v>2644</v>
       </c>
-      <c r="B22" s="20" t="s">
+      <c r="C22" s="20" t="s">
         <v>2645</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="D22" s="20" t="s">
         <v>2646</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>2647</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="42">
       <c r="A23" s="20" t="s">
+        <v>2667</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>2668</v>
+      </c>
+      <c r="C23" s="20" t="s">
         <v>2669</v>
       </c>
-      <c r="B23" s="20" t="s">
+      <c r="D23" s="20" t="s">
         <v>2670</v>
-      </c>
-      <c r="C23" s="20" t="s">
-        <v>2671</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>2672</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="98">
       <c r="A24" s="20" t="s">
+        <v>2678</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>2679</v>
+      </c>
+      <c r="C24" s="20" t="s">
         <v>2680</v>
       </c>
-      <c r="B24" s="20" t="s">
+      <c r="D24" s="20" t="s">
         <v>2681</v>
       </c>
-      <c r="C24" s="20" t="s">
-        <v>2682</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>2683</v>
+    </row>
+    <row r="25" spans="1:4" ht="56">
+      <c r="A25" s="20" t="s">
+        <v>2699</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>2700</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>2701</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>2702</v>
       </c>
     </row>
   </sheetData>
@@ -34603,7 +38039,7 @@
         <v>1204</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>2656</v>
+        <v>2654</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>1176</v>
@@ -34632,7 +38068,7 @@
         <v>1208</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>1176</v>
@@ -34845,7 +38281,7 @@
         <v>1238</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>2663</v>
+        <v>2661</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>1176</v>
@@ -34944,7 +38380,7 @@
         <v>1192</v>
       </c>
       <c r="J21" s="13" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K21" s="1">
         <v>21</v>
@@ -35222,7 +38658,7 @@
         <v>1286</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>2629</v>
+        <v>2628</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>1176</v>
@@ -36232,13 +39668,13 @@
         <v>1423</v>
       </c>
       <c r="B66" t="s">
+        <v>2528</v>
+      </c>
+      <c r="C66" t="s">
         <v>2529</v>
       </c>
-      <c r="C66" t="s">
+      <c r="D66" t="s">
         <v>2530</v>
-      </c>
-      <c r="D66" t="s">
-        <v>2531</v>
       </c>
       <c r="E66" t="s">
         <v>1405</v>
@@ -36247,7 +39683,7 @@
         <v>1192</v>
       </c>
       <c r="J66" t="s">
-        <v>2532</v>
+        <v>2531</v>
       </c>
     </row>
     <row r="67" spans="1:10">
@@ -36255,13 +39691,13 @@
         <v>1425</v>
       </c>
       <c r="B67" t="s">
-        <v>2529</v>
+        <v>2528</v>
       </c>
       <c r="C67" t="s">
+        <v>2532</v>
+      </c>
+      <c r="D67" t="s">
         <v>2533</v>
-      </c>
-      <c r="D67" t="s">
-        <v>2534</v>
       </c>
       <c r="E67" t="s">
         <v>1405</v>
@@ -36270,21 +39706,21 @@
         <v>1192</v>
       </c>
       <c r="J67" t="s">
-        <v>2532</v>
+        <v>2531</v>
       </c>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" s="12" t="s">
-        <v>2499</v>
+        <v>2498</v>
       </c>
       <c r="B68" s="12" t="s">
         <v>485</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>2535</v>
+        <v>2534</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>2657</v>
+        <v>2655</v>
       </c>
       <c r="E68" s="12" t="s">
         <v>1176</v>
@@ -36298,16 +39734,16 @@
     </row>
     <row r="69" spans="1:10">
       <c r="A69" s="12" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="B69" s="12" t="s">
         <v>485</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>2536</v>
+        <v>2535</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>2652</v>
+        <v>2651</v>
       </c>
       <c r="E69" s="12" t="s">
         <v>1176</v>
@@ -36463,7 +39899,7 @@
         <v>1435</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>2664</v>
+        <v>2662</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="24" customHeight="1">
@@ -36902,7 +40338,7 @@
         <v>1483</v>
       </c>
       <c r="H24" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -36922,7 +40358,7 @@
         <v>1483</v>
       </c>
       <c r="H25" t="s">
-        <v>2538</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -36942,7 +40378,7 @@
         <v>1488</v>
       </c>
       <c r="H26" t="s">
-        <v>2539</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -36965,7 +40401,7 @@
         <v>1490</v>
       </c>
       <c r="H27" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -36988,7 +40424,7 @@
         <v>1490</v>
       </c>
       <c r="H28" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -37011,7 +40447,7 @@
         <v>1490</v>
       </c>
       <c r="H29" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -37034,7 +40470,7 @@
         <v>1490</v>
       </c>
       <c r="H30" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -37057,7 +40493,7 @@
         <v>1490</v>
       </c>
       <c r="H31" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -37080,7 +40516,7 @@
         <v>1490</v>
       </c>
       <c r="H32" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -37103,7 +40539,7 @@
         <v>1490</v>
       </c>
       <c r="H33" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -37126,7 +40562,7 @@
         <v>1490</v>
       </c>
       <c r="H34" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -37134,7 +40570,7 @@
         <v>1203</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>1434</v>
@@ -37149,7 +40585,7 @@
         <v>1483</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>2658</v>
+        <v>2656</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -37157,7 +40593,7 @@
         <v>1203</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>1427</v>
@@ -37172,7 +40608,7 @@
         <v>1483</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>2548</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -37180,7 +40616,7 @@
         <v>1203</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>1427</v>
@@ -37195,7 +40631,7 @@
         <v>1483</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>2659</v>
+        <v>2657</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -37203,7 +40639,7 @@
         <v>1207</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>2504</v>
+        <v>2503</v>
       </c>
       <c r="C38" s="12" t="s">
         <v>1434</v>
@@ -37218,15 +40654,15 @@
         <v>1483</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>2660</v>
+        <v>2658</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="12" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="C39" s="12" t="s">
         <v>1441</v>
@@ -37241,7 +40677,7 @@
         <v>1483</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
     </row>
   </sheetData>
@@ -44409,13 +47845,13 @@
         <v>1941</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="C39" s="16" t="s">
+        <v>2549</v>
+      </c>
+      <c r="D39" s="16" t="s">
         <v>2550</v>
-      </c>
-      <c r="D39" s="16" t="s">
-        <v>2551</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -44454,10 +47890,10 @@
         <v>1951</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>2661</v>
+        <v>2659</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>2662</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="28">
@@ -44552,10 +47988,10 @@
         <v>1977</v>
       </c>
       <c r="C49" s="17" t="s">
+        <v>2629</v>
+      </c>
+      <c r="D49" s="17" t="s">
         <v>2630</v>
-      </c>
-      <c r="D49" s="17" t="s">
-        <v>2631</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="28">
@@ -44563,27 +47999,41 @@
         <v>1978</v>
       </c>
       <c r="B50" s="16" t="s">
+        <v>2551</v>
+      </c>
+      <c r="C50" s="16" t="s">
         <v>2552</v>
       </c>
-      <c r="C50" s="16" t="s">
+      <c r="D50" s="16" t="s">
         <v>2553</v>
-      </c>
-      <c r="D50" s="16" t="s">
-        <v>2554</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="28">
       <c r="A51" s="17" t="s">
+        <v>2663</v>
+      </c>
+      <c r="B51" s="17" t="s">
+        <v>2664</v>
+      </c>
+      <c r="C51" s="17" t="s">
         <v>2665</v>
       </c>
-      <c r="B51" s="17" t="s">
+      <c r="D51" s="17" t="s">
         <v>2666</v>
       </c>
-      <c r="C51" s="17" t="s">
-        <v>2667</v>
-      </c>
-      <c r="D51" s="17" t="s">
-        <v>2668</v>
+    </row>
+    <row r="52" spans="1:4" ht="42">
+      <c r="A52" s="17" t="s">
+        <v>2695</v>
+      </c>
+      <c r="B52" s="17" t="s">
+        <v>2696</v>
+      </c>
+      <c r="C52" s="17" t="s">
+        <v>2697</v>
+      </c>
+      <c r="D52" s="17" t="s">
+        <v>2698</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -44770,7 +48220,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
-  <dimension ref="A1:M173"/>
+  <dimension ref="A1:M176"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -46112,7 +49562,7 @@
         <v>838</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>2675</v>
+        <v>2673</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>1991</v>
@@ -46137,7 +49587,7 @@
         <v>1995</v>
       </c>
       <c r="L36" s="21" t="s">
-        <v>2676</v>
+        <v>2674</v>
       </c>
       <c r="M36" s="8">
         <v>36</v>
@@ -47260,10 +50710,10 @@
         <v>1991</v>
       </c>
       <c r="E66" s="21" t="s">
-        <v>2673</v>
+        <v>2671</v>
       </c>
       <c r="F66" s="21" t="s">
-        <v>2674</v>
+        <v>2672</v>
       </c>
       <c r="G66" s="11" t="s">
         <v>2199</v>
@@ -48478,7 +51928,7 @@
         <v>838</v>
       </c>
       <c r="C98" s="21" t="s">
-        <v>2675</v>
+        <v>2673</v>
       </c>
       <c r="D98" s="8" t="s">
         <v>1991</v>
@@ -48501,7 +51951,7 @@
         <v>2051</v>
       </c>
       <c r="L98" s="21" t="s">
-        <v>2677</v>
+        <v>2675</v>
       </c>
       <c r="M98" s="8">
         <v>123</v>
@@ -50235,7 +53685,7 @@
         <v>838</v>
       </c>
       <c r="C145" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D145" t="s">
         <v>1991</v>
@@ -50247,10 +53697,10 @@
         <v>1485</v>
       </c>
       <c r="G145" t="s">
+        <v>2555</v>
+      </c>
+      <c r="H145" t="s">
         <v>2556</v>
-      </c>
-      <c r="H145" t="s">
-        <v>2557</v>
       </c>
       <c r="I145" t="s">
         <v>951</v>
@@ -50259,7 +53709,7 @@
         <v>2444</v>
       </c>
       <c r="L145" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M145">
         <v>173</v>
@@ -50273,7 +53723,7 @@
         <v>838</v>
       </c>
       <c r="C146" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D146" t="s">
         <v>1991</v>
@@ -50285,16 +53735,16 @@
         <v>2004</v>
       </c>
       <c r="G146" t="s">
+        <v>2558</v>
+      </c>
+      <c r="H146" t="s">
         <v>2559</v>
-      </c>
-      <c r="H146" t="s">
-        <v>2560</v>
       </c>
       <c r="K146" t="s">
         <v>2446</v>
       </c>
       <c r="L146" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M146">
         <v>174</v>
@@ -50308,7 +53758,7 @@
         <v>838</v>
       </c>
       <c r="C147" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D147" t="s">
         <v>1991</v>
@@ -50320,16 +53770,16 @@
         <v>2004</v>
       </c>
       <c r="G147" t="s">
+        <v>2560</v>
+      </c>
+      <c r="H147" t="s">
         <v>2561</v>
-      </c>
-      <c r="H147" t="s">
-        <v>2562</v>
       </c>
       <c r="K147" t="s">
         <v>2448</v>
       </c>
       <c r="L147" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M147">
         <v>175</v>
@@ -50343,7 +53793,7 @@
         <v>838</v>
       </c>
       <c r="C148" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D148" t="s">
         <v>1991</v>
@@ -50355,16 +53805,16 @@
         <v>2004</v>
       </c>
       <c r="G148" t="s">
+        <v>2562</v>
+      </c>
+      <c r="H148" t="s">
         <v>2563</v>
-      </c>
-      <c r="H148" t="s">
-        <v>2564</v>
       </c>
       <c r="K148" t="s">
         <v>1524</v>
       </c>
       <c r="L148" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M148">
         <v>176</v>
@@ -50378,7 +53828,7 @@
         <v>838</v>
       </c>
       <c r="C149" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D149" t="s">
         <v>1991</v>
@@ -50390,16 +53840,16 @@
         <v>1485</v>
       </c>
       <c r="G149" t="s">
+        <v>2564</v>
+      </c>
+      <c r="H149" t="s">
         <v>2565</v>
-      </c>
-      <c r="H149" t="s">
-        <v>2566</v>
       </c>
       <c r="K149" t="s">
         <v>2451</v>
       </c>
       <c r="L149" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M149">
         <v>177</v>
@@ -50413,7 +53863,7 @@
         <v>838</v>
       </c>
       <c r="C150" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D150" t="s">
         <v>1991</v>
@@ -50425,16 +53875,16 @@
         <v>1485</v>
       </c>
       <c r="G150" t="s">
+        <v>2566</v>
+      </c>
+      <c r="H150" t="s">
         <v>2567</v>
-      </c>
-      <c r="H150" t="s">
-        <v>2568</v>
       </c>
       <c r="K150" t="s">
         <v>2453</v>
       </c>
       <c r="L150" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M150">
         <v>178</v>
@@ -50448,7 +53898,7 @@
         <v>838</v>
       </c>
       <c r="C151" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D151" t="s">
         <v>1991</v>
@@ -50460,16 +53910,16 @@
         <v>1485</v>
       </c>
       <c r="G151" t="s">
+        <v>2568</v>
+      </c>
+      <c r="H151" t="s">
         <v>2569</v>
-      </c>
-      <c r="H151" t="s">
-        <v>2570</v>
       </c>
       <c r="K151" t="s">
         <v>2453</v>
       </c>
       <c r="L151" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M151">
         <v>179</v>
@@ -50483,7 +53933,7 @@
         <v>838</v>
       </c>
       <c r="C152" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D152" t="s">
         <v>1991</v>
@@ -50495,16 +53945,16 @@
         <v>1485</v>
       </c>
       <c r="G152" t="s">
+        <v>2570</v>
+      </c>
+      <c r="H152" t="s">
         <v>2571</v>
-      </c>
-      <c r="H152" t="s">
-        <v>2572</v>
       </c>
       <c r="K152" t="s">
         <v>2456</v>
       </c>
       <c r="L152" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M152">
         <v>180</v>
@@ -50518,7 +53968,7 @@
         <v>838</v>
       </c>
       <c r="C153" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D153" t="s">
         <v>1991</v>
@@ -50530,16 +53980,16 @@
         <v>1485</v>
       </c>
       <c r="G153" t="s">
+        <v>2572</v>
+      </c>
+      <c r="H153" t="s">
         <v>2573</v>
-      </c>
-      <c r="H153" t="s">
-        <v>2574</v>
       </c>
       <c r="K153" t="s">
         <v>2458</v>
       </c>
       <c r="L153" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M153">
         <v>181</v>
@@ -50553,7 +54003,7 @@
         <v>838</v>
       </c>
       <c r="C154" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D154" t="s">
         <v>1991</v>
@@ -50565,16 +54015,16 @@
         <v>1992</v>
       </c>
       <c r="G154" t="s">
+        <v>2574</v>
+      </c>
+      <c r="H154" t="s">
         <v>2575</v>
-      </c>
-      <c r="H154" t="s">
-        <v>2576</v>
       </c>
       <c r="K154" t="s">
         <v>2446</v>
       </c>
       <c r="L154" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M154">
         <v>182</v>
@@ -50588,7 +54038,7 @@
         <v>838</v>
       </c>
       <c r="C155" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D155" t="s">
         <v>1991</v>
@@ -50600,16 +54050,16 @@
         <v>1992</v>
       </c>
       <c r="G155" t="s">
+        <v>2576</v>
+      </c>
+      <c r="H155" t="s">
         <v>2577</v>
-      </c>
-      <c r="H155" t="s">
-        <v>2578</v>
       </c>
       <c r="K155" t="s">
         <v>2444</v>
       </c>
       <c r="L155" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M155">
         <v>183</v>
@@ -50623,7 +54073,7 @@
         <v>838</v>
       </c>
       <c r="C156" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D156" t="s">
         <v>1991</v>
@@ -50635,16 +54085,16 @@
         <v>1485</v>
       </c>
       <c r="G156" t="s">
+        <v>2578</v>
+      </c>
+      <c r="H156" t="s">
         <v>2579</v>
-      </c>
-      <c r="H156" t="s">
-        <v>2580</v>
       </c>
       <c r="K156" t="s">
         <v>2446</v>
       </c>
       <c r="L156" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M156">
         <v>184</v>
@@ -50658,7 +54108,7 @@
         <v>838</v>
       </c>
       <c r="C157" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D157" t="s">
         <v>1991</v>
@@ -50670,10 +54120,10 @@
         <v>2004</v>
       </c>
       <c r="G157" t="s">
+        <v>2580</v>
+      </c>
+      <c r="H157" t="s">
         <v>2581</v>
-      </c>
-      <c r="H157" t="s">
-        <v>2582</v>
       </c>
       <c r="I157" t="s">
         <v>953</v>
@@ -50682,7 +54132,7 @@
         <v>2444</v>
       </c>
       <c r="L157" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M157">
         <v>185</v>
@@ -50696,7 +54146,7 @@
         <v>838</v>
       </c>
       <c r="C158" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D158" t="s">
         <v>1991</v>
@@ -50708,10 +54158,10 @@
         <v>1485</v>
       </c>
       <c r="G158" t="s">
+        <v>2582</v>
+      </c>
+      <c r="H158" t="s">
         <v>2583</v>
-      </c>
-      <c r="H158" t="s">
-        <v>2584</v>
       </c>
       <c r="I158" t="s">
         <v>951</v>
@@ -50720,7 +54170,7 @@
         <v>2444</v>
       </c>
       <c r="L158" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M158">
         <v>186</v>
@@ -50734,7 +54184,7 @@
         <v>838</v>
       </c>
       <c r="C159" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D159" t="s">
         <v>1991</v>
@@ -50746,16 +54196,16 @@
         <v>2004</v>
       </c>
       <c r="G159" t="s">
+        <v>2584</v>
+      </c>
+      <c r="H159" t="s">
         <v>2585</v>
-      </c>
-      <c r="H159" t="s">
-        <v>2586</v>
       </c>
       <c r="K159" t="s">
         <v>2451</v>
       </c>
       <c r="L159" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M159">
         <v>187</v>
@@ -50769,7 +54219,7 @@
         <v>838</v>
       </c>
       <c r="C160" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D160" t="s">
         <v>1991</v>
@@ -50781,16 +54231,16 @@
         <v>1485</v>
       </c>
       <c r="G160" t="s">
+        <v>2586</v>
+      </c>
+      <c r="H160" t="s">
         <v>2587</v>
-      </c>
-      <c r="H160" t="s">
-        <v>2588</v>
       </c>
       <c r="K160" t="s">
         <v>2466</v>
       </c>
       <c r="L160" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M160">
         <v>188</v>
@@ -50804,7 +54254,7 @@
         <v>838</v>
       </c>
       <c r="C161" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D161" t="s">
         <v>1991</v>
@@ -50816,16 +54266,16 @@
         <v>1485</v>
       </c>
       <c r="G161" t="s">
+        <v>2588</v>
+      </c>
+      <c r="H161" t="s">
         <v>2589</v>
-      </c>
-      <c r="H161" t="s">
-        <v>2590</v>
       </c>
       <c r="K161" t="s">
         <v>1524</v>
       </c>
       <c r="L161" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M161">
         <v>189</v>
@@ -50839,7 +54289,7 @@
         <v>838</v>
       </c>
       <c r="C162" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D162" t="s">
         <v>1991</v>
@@ -50851,16 +54301,16 @@
         <v>2004</v>
       </c>
       <c r="G162" t="s">
+        <v>2590</v>
+      </c>
+      <c r="H162" t="s">
         <v>2591</v>
-      </c>
-      <c r="H162" t="s">
-        <v>2592</v>
       </c>
       <c r="K162" t="s">
         <v>1524</v>
       </c>
       <c r="L162" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M162">
         <v>190</v>
@@ -50874,7 +54324,7 @@
         <v>838</v>
       </c>
       <c r="C163" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D163" t="s">
         <v>1991</v>
@@ -50886,16 +54336,16 @@
         <v>1992</v>
       </c>
       <c r="G163" t="s">
+        <v>2592</v>
+      </c>
+      <c r="H163" t="s">
         <v>2593</v>
-      </c>
-      <c r="H163" t="s">
-        <v>2594</v>
       </c>
       <c r="K163" t="s">
         <v>1524</v>
       </c>
       <c r="L163" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M163">
         <v>191</v>
@@ -50909,7 +54359,7 @@
         <v>838</v>
       </c>
       <c r="C164" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D164" t="s">
         <v>1991</v>
@@ -50921,16 +54371,16 @@
         <v>1485</v>
       </c>
       <c r="G164" t="s">
+        <v>2594</v>
+      </c>
+      <c r="H164" t="s">
         <v>2595</v>
-      </c>
-      <c r="H164" t="s">
-        <v>2596</v>
       </c>
       <c r="K164" t="s">
         <v>1995</v>
       </c>
       <c r="L164" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M164">
         <v>192</v>
@@ -50944,7 +54394,7 @@
         <v>838</v>
       </c>
       <c r="C165" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D165" t="s">
         <v>1991</v>
@@ -50956,16 +54406,16 @@
         <v>1485</v>
       </c>
       <c r="G165" t="s">
+        <v>2596</v>
+      </c>
+      <c r="H165" t="s">
         <v>2597</v>
-      </c>
-      <c r="H165" t="s">
-        <v>2598</v>
       </c>
       <c r="K165" t="s">
         <v>2453</v>
       </c>
       <c r="L165" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M165">
         <v>193</v>
@@ -50979,7 +54429,7 @@
         <v>838</v>
       </c>
       <c r="C166" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D166" t="s">
         <v>1991</v>
@@ -50991,16 +54441,16 @@
         <v>1992</v>
       </c>
       <c r="G166" t="s">
+        <v>2598</v>
+      </c>
+      <c r="H166" t="s">
         <v>2599</v>
-      </c>
-      <c r="H166" t="s">
-        <v>2600</v>
       </c>
       <c r="K166" t="s">
         <v>2453</v>
       </c>
       <c r="L166" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M166">
         <v>194</v>
@@ -51014,7 +54464,7 @@
         <v>838</v>
       </c>
       <c r="C167" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D167" t="s">
         <v>1991</v>
@@ -51026,16 +54476,16 @@
         <v>1485</v>
       </c>
       <c r="G167" t="s">
+        <v>2600</v>
+      </c>
+      <c r="H167" t="s">
         <v>2601</v>
-      </c>
-      <c r="H167" t="s">
-        <v>2602</v>
       </c>
       <c r="K167" t="s">
         <v>2458</v>
       </c>
       <c r="L167" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M167">
         <v>196</v>
@@ -51049,7 +54499,7 @@
         <v>838</v>
       </c>
       <c r="C168" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D168" t="s">
         <v>1991</v>
@@ -51061,16 +54511,16 @@
         <v>1485</v>
       </c>
       <c r="G168" t="s">
+        <v>2602</v>
+      </c>
+      <c r="H168" t="s">
         <v>2603</v>
-      </c>
-      <c r="H168" t="s">
-        <v>2604</v>
       </c>
       <c r="K168" t="s">
         <v>1524</v>
       </c>
       <c r="L168" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M168">
         <v>197</v>
@@ -51084,7 +54534,7 @@
         <v>838</v>
       </c>
       <c r="C169" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D169" t="s">
         <v>1991</v>
@@ -51096,16 +54546,16 @@
         <v>1992</v>
       </c>
       <c r="G169" t="s">
+        <v>2604</v>
+      </c>
+      <c r="H169" t="s">
         <v>2605</v>
-      </c>
-      <c r="H169" t="s">
-        <v>2606</v>
       </c>
       <c r="K169" t="s">
         <v>2444</v>
       </c>
       <c r="L169" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M169">
         <v>198</v>
@@ -51119,7 +54569,7 @@
         <v>838</v>
       </c>
       <c r="C170" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D170" t="s">
         <v>1991</v>
@@ -51131,16 +54581,16 @@
         <v>1485</v>
       </c>
       <c r="G170" t="s">
+        <v>2606</v>
+      </c>
+      <c r="H170" t="s">
         <v>2607</v>
-      </c>
-      <c r="H170" t="s">
-        <v>2608</v>
       </c>
       <c r="K170" t="s">
         <v>2446</v>
       </c>
       <c r="L170" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M170">
         <v>199</v>
@@ -51154,7 +54604,7 @@
         <v>838</v>
       </c>
       <c r="C171" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D171" t="s">
         <v>1991</v>
@@ -51166,10 +54616,10 @@
         <v>1485</v>
       </c>
       <c r="G171" t="s">
+        <v>2608</v>
+      </c>
+      <c r="H171" t="s">
         <v>2609</v>
-      </c>
-      <c r="H171" t="s">
-        <v>2610</v>
       </c>
       <c r="I171" t="s">
         <v>951</v>
@@ -51178,7 +54628,7 @@
         <v>2446</v>
       </c>
       <c r="L171" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M171">
         <v>200</v>
@@ -51192,7 +54642,7 @@
         <v>838</v>
       </c>
       <c r="C172" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D172" t="s">
         <v>1991</v>
@@ -51204,16 +54654,16 @@
         <v>2004</v>
       </c>
       <c r="G172" t="s">
+        <v>2610</v>
+      </c>
+      <c r="H172" t="s">
         <v>2611</v>
-      </c>
-      <c r="H172" t="s">
-        <v>2612</v>
       </c>
       <c r="K172" t="s">
         <v>1995</v>
       </c>
       <c r="L172" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M172">
         <v>201</v>
@@ -51227,7 +54677,7 @@
         <v>838</v>
       </c>
       <c r="C173" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D173" t="s">
         <v>1991</v>
@@ -51239,19 +54689,124 @@
         <v>1992</v>
       </c>
       <c r="G173" t="s">
+        <v>2612</v>
+      </c>
+      <c r="H173" t="s">
         <v>2613</v>
-      </c>
-      <c r="H173" t="s">
-        <v>2614</v>
       </c>
       <c r="K173" t="s">
         <v>1524</v>
       </c>
       <c r="L173" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M173">
         <v>202</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13">
+      <c r="A174" s="12" t="s">
+        <v>2682</v>
+      </c>
+      <c r="B174" s="12" t="s">
+        <v>838</v>
+      </c>
+      <c r="C174" s="12" t="s">
+        <v>1990</v>
+      </c>
+      <c r="D174" s="12" t="s">
+        <v>2078</v>
+      </c>
+      <c r="E174" s="12"/>
+      <c r="F174" s="12"/>
+      <c r="G174" s="12" t="s">
+        <v>2683</v>
+      </c>
+      <c r="H174" s="12" t="s">
+        <v>2684</v>
+      </c>
+      <c r="I174" s="12" t="s">
+        <v>952</v>
+      </c>
+      <c r="J174" s="12"/>
+      <c r="K174" s="12" t="s">
+        <v>1995</v>
+      </c>
+      <c r="L174" s="12" t="s">
+        <v>2685</v>
+      </c>
+      <c r="M174" s="12">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="175" spans="1:13">
+      <c r="A175" s="12" t="s">
+        <v>2687</v>
+      </c>
+      <c r="B175" s="12" t="s">
+        <v>838</v>
+      </c>
+      <c r="C175" s="12" t="s">
+        <v>1990</v>
+      </c>
+      <c r="D175" s="12" t="s">
+        <v>2078</v>
+      </c>
+      <c r="E175" s="12"/>
+      <c r="F175" s="12"/>
+      <c r="G175" s="12" t="s">
+        <v>2688</v>
+      </c>
+      <c r="H175" s="12" t="s">
+        <v>2689</v>
+      </c>
+      <c r="I175" s="12" t="s">
+        <v>952</v>
+      </c>
+      <c r="J175" s="12"/>
+      <c r="K175" s="12" t="s">
+        <v>1995</v>
+      </c>
+      <c r="L175" s="12" t="s">
+        <v>2685</v>
+      </c>
+      <c r="M175" s="12">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="176" spans="1:13">
+      <c r="A176" s="12" t="s">
+        <v>2690</v>
+      </c>
+      <c r="B176" s="12" t="s">
+        <v>838</v>
+      </c>
+      <c r="C176" s="12" t="s">
+        <v>1990</v>
+      </c>
+      <c r="D176" s="12" t="s">
+        <v>2078</v>
+      </c>
+      <c r="E176" s="12"/>
+      <c r="F176" s="12"/>
+      <c r="G176" s="12" t="s">
+        <v>2691</v>
+      </c>
+      <c r="H176" s="12" t="s">
+        <v>2692</v>
+      </c>
+      <c r="I176" s="12" t="s">
+        <v>952</v>
+      </c>
+      <c r="J176" s="12"/>
+      <c r="K176" s="12" t="s">
+        <v>1995</v>
+      </c>
+      <c r="L176" s="12" t="s">
+        <v>2685</v>
+      </c>
+      <c r="M176" s="12">
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -51265,7 +54820,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
-  <dimension ref="A1:K173"/>
+  <dimension ref="A1:K176"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -52067,8 +55622,8 @@
       <c r="F27" s="8" t="s">
         <v>326</v>
       </c>
-      <c r="G27" s="9" t="b">
-        <v>0</v>
+      <c r="G27" s="22" t="b">
+        <v>1</v>
       </c>
       <c r="H27" s="8" t="s">
         <v>334</v>
@@ -56029,7 +59584,7 @@
         <v>838</v>
       </c>
       <c r="C156" t="s">
-        <v>2615</v>
+        <v>2614</v>
       </c>
       <c r="D156" t="s">
         <v>2496</v>
@@ -56058,7 +59613,7 @@
         <v>838</v>
       </c>
       <c r="C157" t="s">
-        <v>2615</v>
+        <v>2614</v>
       </c>
       <c r="D157" t="s">
         <v>2496</v>
@@ -56406,13 +59961,13 @@
         <v>838</v>
       </c>
       <c r="C169" s="12" t="s">
-        <v>2679</v>
+        <v>2677</v>
       </c>
       <c r="D169" t="s">
         <v>326</v>
       </c>
       <c r="E169" s="12" t="s">
-        <v>2678</v>
+        <v>2676</v>
       </c>
       <c r="F169" t="s">
         <v>326</v>
@@ -56464,7 +60019,7 @@
         <v>838</v>
       </c>
       <c r="C171" t="s">
-        <v>2615</v>
+        <v>2614</v>
       </c>
       <c r="D171" t="s">
         <v>2496</v>
@@ -56541,6 +60096,99 @@
       </c>
       <c r="K173">
         <v>202</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11">
+      <c r="A174" s="12" t="s">
+        <v>2682</v>
+      </c>
+      <c r="B174" s="12" t="s">
+        <v>838</v>
+      </c>
+      <c r="C174" s="12" t="s">
+        <v>2686</v>
+      </c>
+      <c r="D174" s="12" t="s">
+        <v>2496</v>
+      </c>
+      <c r="E174" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="F174" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="G174" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H174" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="I174" s="12"/>
+      <c r="J174" s="12"/>
+      <c r="K174" s="12">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11">
+      <c r="A175" s="12" t="s">
+        <v>2687</v>
+      </c>
+      <c r="B175" s="12" t="s">
+        <v>838</v>
+      </c>
+      <c r="C175" s="12" t="s">
+        <v>2686</v>
+      </c>
+      <c r="D175" s="12" t="s">
+        <v>2496</v>
+      </c>
+      <c r="E175" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="F175" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="G175" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H175" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="I175" s="12"/>
+      <c r="J175" s="12"/>
+      <c r="K175" s="12">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11">
+      <c r="A176" s="12" t="s">
+        <v>2690</v>
+      </c>
+      <c r="B176" s="12" t="s">
+        <v>838</v>
+      </c>
+      <c r="C176" s="12" t="s">
+        <v>2686</v>
+      </c>
+      <c r="D176" s="12" t="s">
+        <v>2496</v>
+      </c>
+      <c r="E176" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="F176" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="G176" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H176" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="I176" s="12"/>
+      <c r="J176" s="12"/>
+      <c r="K176" s="12">
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -57087,7 +60735,7 @@
         <v>292</v>
       </c>
       <c r="I23" t="s">
-        <v>2517</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="24" customHeight="1">
@@ -58780,7 +62428,7 @@
         <v>449</v>
       </c>
       <c r="I100" t="s">
-        <v>2518</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="24" customHeight="1">
@@ -59285,7 +62933,7 @@
         <v>482</v>
       </c>
       <c r="I123" t="s">
-        <v>2519</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="24" customHeight="1">
@@ -59377,7 +63025,7 @@
         <v>292</v>
       </c>
       <c r="I127" t="s">
-        <v>2517</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="24" customHeight="1">
@@ -59678,7 +63326,7 @@
         <v>292</v>
       </c>
       <c r="I141" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="24" customHeight="1">
@@ -59793,7 +63441,7 @@
         <v>518</v>
       </c>
       <c r="I146" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="24" customHeight="1">
@@ -63226,7 +66874,7 @@
         <v>802</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>2636</v>
+        <v>2635</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>803</v>
@@ -63263,7 +66911,7 @@
         <v>810</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>811</v>
@@ -63272,10 +66920,10 @@
         <v>812</v>
       </c>
       <c r="E4" s="6" t="s">
+        <v>2522</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>2523</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>2524</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>427</v>
@@ -63318,7 +66966,7 @@
         <v>820</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>2655</v>
+        <v>2693</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>821</v>
@@ -63401,19 +67049,19 @@
         <v>835</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>836</v>
       </c>
       <c r="D10" s="6" t="s">
+        <v>2525</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>2526</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="F10" s="6" t="s">
         <v>2527</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>2528</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>427</v>
@@ -63493,7 +67141,7 @@
         <v>841</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>2637</v>
+        <v>2636</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>842</v>
@@ -63519,16 +67167,16 @@
         <v>846</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>2648</v>
+        <v>2647</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>847</v>
       </c>
       <c r="G3" s="13" t="s">
+        <v>2648</v>
+      </c>
+      <c r="H3" s="13" t="s">
         <v>2649</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>2650</v>
       </c>
       <c r="I3" s="1">
         <v>3</v>
@@ -63548,7 +67196,7 @@
         <v>846</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>2626</v>
+        <v>2625</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>847</v>
@@ -63577,7 +67225,7 @@
         <v>846</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>2616</v>
+        <v>2615</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>847</v>
@@ -63606,16 +67254,16 @@
         <v>846</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>2617</v>
+        <v>2616</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>858</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>2632</v>
+        <v>2631</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>2618</v>
+        <v>2617</v>
       </c>
       <c r="I6" s="1">
         <v>6</v>
@@ -63635,7 +67283,7 @@
         <v>846</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>2627</v>
+        <v>2626</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>847</v>
@@ -63664,7 +67312,7 @@
         <v>846</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>2619</v>
+        <v>2618</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>847</v>
@@ -63693,7 +67341,7 @@
         <v>846</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>2620</v>
+        <v>2619</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>847</v>
@@ -63722,16 +67370,16 @@
         <v>873</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>2638</v>
+        <v>2637</v>
       </c>
       <c r="F10" t="s">
         <v>874</v>
       </c>
       <c r="G10" s="12" t="s">
+        <v>2638</v>
+      </c>
+      <c r="H10" s="12" t="s">
         <v>2639</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>2640</v>
       </c>
     </row>
   </sheetData>
@@ -63842,7 +67490,7 @@
         <v>879</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>2628</v>
+        <v>2627</v>
       </c>
       <c r="F4" s="1">
         <v>-1</v>
@@ -63865,7 +67513,7 @@
         <v>880</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>2651</v>
+        <v>2650</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
@@ -63888,7 +67536,7 @@
         <v>881</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>2634</v>
+        <v>2633</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -63911,7 +67559,7 @@
         <v>882</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>2633</v>
+        <v>2632</v>
       </c>
       <c r="F7" s="1">
         <v>-1</v>
@@ -64003,7 +67651,7 @@
         <v>882</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>2633</v>
+        <v>2632</v>
       </c>
       <c r="F11" s="1">
         <v>1</v>
@@ -64072,7 +67720,7 @@
         <v>882</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>2633</v>
+        <v>2632</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1">
@@ -64090,10 +67738,10 @@
         <v>2</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>2634</v>
+        <v>2633</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1">
@@ -64111,10 +67759,10 @@
         <v>3</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>2622</v>
+        <v>2621</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>2635</v>
+        <v>2634</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1">
@@ -64342,7 +67990,7 @@
         <v>904</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>2641</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -64376,7 +68024,7 @@
         <v>907</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
   </sheetData>
@@ -65598,18 +69246,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -65631,18 +69279,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA5F7BAD-F7AB-4266-8370-535EF14A9159}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/files/diet-data-contract-v1.0.1.xlsx
+++ b/files/diet-data-contract-v1.0.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{486D83BE-DC1F-4D17-A145-17307EF39B54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE52BCFB-9C40-425D-B39A-20AAEA82796F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8162" uniqueCount="2703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8195" uniqueCount="2714">
   <si>
     <t>항목</t>
   </si>
@@ -31698,6 +31698,3107 @@
     </r>
   </si>
   <si>
+    <t>V-52</t>
+  </si>
+  <si>
+    <r>
+      <t>저녁</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>우선</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>17시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이후에도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>고정</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>「조금</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적게」「거의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>못</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹거나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>걸렀어요」이면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>풀을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먼저</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>쓴다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이때는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가능</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(after_dinner_eligible=true)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>인</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>후보로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>하고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그날</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질환</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>금지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>성격</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시간</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>달력</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>조건을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>다시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적용한다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>후보가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>하나도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>남지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않으면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>넘어간다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>저녁에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대상</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>했는데</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가능</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>있는데도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>나오지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않으면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>거부</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>저녁</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>추가</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>저녁</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(17</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>에는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가능</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>쓰는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>때문에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 0</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개라</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>「조금</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적게」「거의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>못</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹거나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>걸렀어요」를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답해도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>나오지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않음</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>다음</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가능으로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>바꾸고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>자정</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>추가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>출출하면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가볍게</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>요기하기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>따뜻한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>우유나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두유</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>잔</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>내일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙길</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>것</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>준비하기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>저녁에도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먼저</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>쓰고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번갈아</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>나옴</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>후보</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 13</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>→</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 17</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(17~24</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 17</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>, 00~04</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>목표문구</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>노출조건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DIET-P-0033, 0269~0271 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>구현기준</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> R-05 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>검증규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> V-52 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>참조설정데이터</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구세트</t>
+    </r>
+  </si>
+  <si>
+    <t>DIET-P-0272</t>
+  </si>
+  <si>
+    <r>
+      <t>입맛</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>날</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적어</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두기</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>식욕이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>떨어지는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>때를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>알면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식사를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>쉬워요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>10-07 추가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>양을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>바꾸지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이라</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>신장질환</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>사용자의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표로도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>쓸</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>있음</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가능</t>
+    </r>
+  </si>
+  <si>
+    <t>DIET-P-0273</t>
+  </si>
+  <si>
+    <r>
+      <t>식사</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시간</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정해</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두기</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>시간이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>일정하면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>놓치기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>어려워요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
     <r>
       <t>17~24시와</t>
     </r>
@@ -31804,6 +34905,1309 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve"> 19</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>후보로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>사용한다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>. 17~24</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 19</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>, 00~04</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>저녁</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전체</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시간대</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(EVENING) 3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개와</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시간</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>제한이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(ANY) 2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>모두</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 5</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>사용한다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>질문 9, 선택지 27, 목표문구 177, 노출조건 177, 질환규칙 14, 상병코드조건 61, 설정 68</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>신장질환도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>받는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>추가</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 10</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>모두</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>증량</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>성격이라</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>만성</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>신장질환</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>사용자는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>「조금</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적게」「거의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>못</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹거나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>걸렀어요」를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답해도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>받지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>못함</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>증량이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아닌</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>추가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>입맛</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>날</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적어</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식사</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시간</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정해</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시간</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>제한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없음</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가능</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">). </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>신장질환</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>사용자도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번갈아</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>받음</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>후보</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve"> 17</t>
     </r>
     <r>
@@ -31832,74 +36236,17 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>문구를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>후보로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>사용한다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>. 17~24</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 17</t>
+      <t>→</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 19</t>
     </r>
     <r>
       <rPr>
@@ -31918,6 +36265,44 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
+      <t>(17~24</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 19</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
       <t>, 00~04</t>
     </r>
     <r>
@@ -31927,700 +36312,41 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>시는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>저녁</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>전체</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시간대</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>(EVENING)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>맞는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 3</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>사용한다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>질문 9, 선택지 27, 목표문구 175, 노출조건 175, 질환규칙 14, 상병코드조건 61, 설정 68</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>V-52</t>
-  </si>
-  <si>
-    <r>
-      <t>저녁</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>회복</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>우선</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>17시</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이후에도</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>고정</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질문</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>답이</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>「조금</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>적게」「거의</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>못</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹거나</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>걸렀어요」이면</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>회복</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>풀을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먼저</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>쓴다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이때는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>식후</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>가능</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>(after_dinner_eligible=true)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>인</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>회복</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구만</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>후보로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>하고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>그날</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질환</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>금지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>성격</t>
+      <t>시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 5</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>목표문구</t>
     </r>
     <r>
       <rPr>
@@ -32639,1808 +36365,6 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>시간</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>달력</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>조건을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>다시</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>적용한다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>회복</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>후보가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>하나도</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>남지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않으면</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>식후</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>넘어간다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>저녁에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>회복</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대상</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>답을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>했는데</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>식후</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>가능</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>회복</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>있는데도</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>회복</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>나오지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않으면</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>거부</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>저녁</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>회복</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>추가</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>저녁</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>(17</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이후</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>에는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>식후</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>가능</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구만</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>쓰는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>규칙</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>때문에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>회복</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 0</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개라</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>「조금</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>적게」「거의</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>못</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹거나</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>걸렀어요」를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>답해도</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>회복</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>나오지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않음</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>다음</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끼니는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>챙기기를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>식후</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>가능으로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>바꾸고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>자정</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>전</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>회복</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 3</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>추가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>출출하면</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>가볍게</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>요기하기</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>따뜻한</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>우유나</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>두유</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>한</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>잔</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>내일</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>아침</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>챙길</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>것</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>준비하기</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>저녁에도</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>회복</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먼저</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>쓰고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>번갈아</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>나옴</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>식후</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>후보</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 13</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>→</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 17</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>(17~24</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 17</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>, 00~04</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 3</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>목표문구</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
       <t>노출조건</t>
     </r>
     <r>
@@ -34470,7 +36394,7 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> DIET-P-0033, 0269~0271 · </t>
+      <t xml:space="preserve"> DIET-P-0272·0273 · </t>
     </r>
     <r>
       <rPr>
@@ -34490,25 +36414,6 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> R-05 · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>검증규칙</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> V-52 · </t>
     </r>
     <r>
       <rPr>
@@ -35059,7 +36964,7 @@
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="58" xr:uid="{00000000-000C-0000-FFFF-FFFF18000000}" name="DietGoalPhrasesClean" displayName="DietGoalPhrasesClean" ref="A1:M176" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="58" xr:uid="{00000000-000C-0000-FFFF-FFFF18000000}" name="DietGoalPhrasesClean" displayName="DietGoalPhrasesClean" ref="A1:M178" totalsRowShown="0">
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-1800-000001000000}" name="phrase_id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-1800-000002000000}" name="phrase_version"/>
@@ -35080,8 +36985,8 @@
 </file>
 
 <file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="59" xr:uid="{00000000-000C-0000-FFFF-FFFF19000000}" name="DietPhraseApplicabilityClean" displayName="DietPhraseApplicabilityClean" ref="A1:K176" totalsRowShown="0">
-  <autoFilter ref="A1:K176" xr:uid="{00000000-000C-0000-FFFF-FFFF19000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="59" xr:uid="{00000000-000C-0000-FFFF-FFFF19000000}" name="DietPhraseApplicabilityClean" displayName="DietPhraseApplicabilityClean" ref="A1:K178" totalsRowShown="0">
+  <autoFilter ref="A1:K178" xr:uid="{00000000-000C-0000-FFFF-FFFF19000000}">
     <filterColumn colId="6">
       <filters>
         <filter val="TRUE"/>
@@ -35408,7 +37313,7 @@
   <sheetPr>
     <tabColor rgb="FF315A7D"/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1"/>
@@ -35500,7 +37405,7 @@
         <v>18</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>2694</v>
+        <v>2709</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="24" customHeight="1">
@@ -35631,16 +37536,30 @@
     </row>
     <row r="25" spans="1:4" ht="56">
       <c r="A25" s="20" t="s">
+        <v>2697</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>2698</v>
+      </c>
+      <c r="C25" s="20" t="s">
         <v>2699</v>
       </c>
-      <c r="B25" s="20" t="s">
+      <c r="D25" s="20" t="s">
         <v>2700</v>
       </c>
-      <c r="C25" s="20" t="s">
-        <v>2701</v>
-      </c>
-      <c r="D25" s="20" t="s">
-        <v>2702</v>
+    </row>
+    <row r="26" spans="1:4" ht="42">
+      <c r="A26" s="20" t="s">
+        <v>2710</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>2711</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>2712</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>2713</v>
       </c>
     </row>
   </sheetData>
@@ -48024,16 +49943,16 @@
     </row>
     <row r="52" spans="1:4" ht="42">
       <c r="A52" s="17" t="s">
+        <v>2693</v>
+      </c>
+      <c r="B52" s="17" t="s">
+        <v>2694</v>
+      </c>
+      <c r="C52" s="17" t="s">
         <v>2695</v>
       </c>
-      <c r="B52" s="17" t="s">
+      <c r="D52" s="17" t="s">
         <v>2696</v>
-      </c>
-      <c r="C52" s="17" t="s">
-        <v>2697</v>
-      </c>
-      <c r="D52" s="17" t="s">
-        <v>2698</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -48220,7 +50139,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
-  <dimension ref="A1:M176"/>
+  <dimension ref="A1:M178"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -54809,6 +56728,70 @@
         <v>205</v>
       </c>
     </row>
+    <row r="177" spans="1:13">
+      <c r="A177" s="12" t="s">
+        <v>2701</v>
+      </c>
+      <c r="B177" s="12" t="s">
+        <v>838</v>
+      </c>
+      <c r="C177" s="12" t="s">
+        <v>1990</v>
+      </c>
+      <c r="D177" s="12" t="s">
+        <v>2078</v>
+      </c>
+      <c r="E177" s="12"/>
+      <c r="F177" s="12"/>
+      <c r="G177" s="12" t="s">
+        <v>2702</v>
+      </c>
+      <c r="H177" s="12" t="s">
+        <v>2703</v>
+      </c>
+      <c r="I177" s="12"/>
+      <c r="J177" s="12"/>
+      <c r="K177" s="12"/>
+      <c r="L177" s="12" t="s">
+        <v>2704</v>
+      </c>
+      <c r="M177" s="12">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="178" spans="1:13">
+      <c r="A178" s="12" t="s">
+        <v>2705</v>
+      </c>
+      <c r="B178" s="12" t="s">
+        <v>838</v>
+      </c>
+      <c r="C178" s="12" t="s">
+        <v>1990</v>
+      </c>
+      <c r="D178" s="12" t="s">
+        <v>2078</v>
+      </c>
+      <c r="E178" s="12"/>
+      <c r="F178" s="12"/>
+      <c r="G178" s="12" t="s">
+        <v>2706</v>
+      </c>
+      <c r="H178" s="12" t="s">
+        <v>2707</v>
+      </c>
+      <c r="I178" s="12"/>
+      <c r="J178" s="12"/>
+      <c r="K178" s="12" t="s">
+        <v>2444</v>
+      </c>
+      <c r="L178" s="12" t="s">
+        <v>2704</v>
+      </c>
+      <c r="M178" s="12">
+        <v>207</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -54820,7 +56803,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
-  <dimension ref="A1:K176"/>
+  <dimension ref="A1:K178"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -60189,6 +62172,68 @@
       <c r="J176" s="12"/>
       <c r="K176" s="12">
         <v>205</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11">
+      <c r="A177" s="12" t="s">
+        <v>2701</v>
+      </c>
+      <c r="B177" s="12" t="s">
+        <v>838</v>
+      </c>
+      <c r="C177" s="12" t="s">
+        <v>2486</v>
+      </c>
+      <c r="D177" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="E177" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="F177" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="G177" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H177" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="I177" s="12"/>
+      <c r="J177" s="12"/>
+      <c r="K177" s="12">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11">
+      <c r="A178" s="12" t="s">
+        <v>2705</v>
+      </c>
+      <c r="B178" s="12" t="s">
+        <v>838</v>
+      </c>
+      <c r="C178" s="12" t="s">
+        <v>2486</v>
+      </c>
+      <c r="D178" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="E178" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="F178" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="G178" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H178" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="I178" s="12"/>
+      <c r="J178" s="12"/>
+      <c r="K178" s="12">
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -66966,7 +69011,7 @@
         <v>820</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>2693</v>
+        <v>2708</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>821</v>
@@ -69246,18 +71291,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -69279,18 +71324,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA5F7BAD-F7AB-4266-8370-535EF14A9159}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/files/diet-data-contract-v1.0.1.xlsx
+++ b/files/diet-data-contract-v1.0.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE52BCFB-9C40-425D-B39A-20AAEA82796F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B3DAD4E-5840-42AA-B62E-ED2D52703A89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34799,459 +34799,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>17~24시와</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 00~04</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>식후</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> READY</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이면서</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> after_dinner_eligible=true</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>인</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 19</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>후보로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>사용한다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>. 17~24</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 19</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>, 00~04</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>저녁</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>전체</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시간대</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>(EVENING) 3</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개와</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시간</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>제한이</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>없는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>(ANY) 2</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>모두</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 5</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>사용한다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>질문 9, 선택지 27, 목표문구 177, 노출조건 177, 질환규칙 14, 상병코드조건 61, 설정 68</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -36443,6 +35990,744 @@
       </rPr>
       <t>문구세트</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t>17~24시와</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 00~04</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> READY</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이면서</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> after_dinner_eligible=true</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>인</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>노출조건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트에서</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> true</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>인</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>줄</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전체</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>후보로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>사용한다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>. 17~24</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>모두</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>쓰고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>, 00~04</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그중</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시간</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>제한이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없거나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(ANY) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>저녁</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전체</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시간대</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(EVENING)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>인</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>쓴다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>늘거나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>줄어도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개수는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문장이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아니라</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>노출조건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>센다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -37405,7 +37690,7 @@
         <v>18</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>2709</v>
+        <v>2708</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="24" customHeight="1">
@@ -37550,16 +37835,16 @@
     </row>
     <row r="26" spans="1:4" ht="42">
       <c r="A26" s="20" t="s">
+        <v>2709</v>
+      </c>
+      <c r="B26" s="20" t="s">
         <v>2710</v>
       </c>
-      <c r="B26" s="20" t="s">
+      <c r="C26" s="20" t="s">
         <v>2711</v>
       </c>
-      <c r="C26" s="20" t="s">
+      <c r="D26" s="20" t="s">
         <v>2712</v>
-      </c>
-      <c r="D26" s="20" t="s">
-        <v>2713</v>
       </c>
     </row>
   </sheetData>
@@ -69011,7 +69296,7 @@
         <v>820</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>2708</v>
+        <v>2713</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>821</v>
@@ -71291,18 +71576,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -71324,18 +71609,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA5F7BAD-F7AB-4266-8370-535EF14A9159}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/files/diet-data-contract-v1.0.1.xlsx
+++ b/files/diet-data-contract-v1.0.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D95292DC-7039-49BB-A977-B818C01AA149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{652C313C-F5F7-45B7-BB44-74442E7FBC0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56315,10 +56315,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>자동 노출 조건은 시간대, 평일·주말, 명절·연휴만 사용한다. 명절·연휴는 달력일자 시트의 날짜(calendar_code HOLIDAY)로 판정한다. 배달·편의점·회식·카페·사무실·급식·마트·야근·여행처럼 앱이 확인하지 않는 상황 조건은 사용하지 않는다.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>목표 축은 그날 회전 질문으로 고른 축과 같다. 그 축에 금지·시간·상황 필터를 통과한 문구가 없을 때만 다음 축으로 내려가며, 그 순서는 직접 선택 → 사용자 확인 진료정보 → 3개월 이내 건강검진 신호 → 일반이다. 끼니 규칙 축도 일반 축에 포함한다. 같은 질환은 직접 선택 출처로 한 번만 반영. 금지 성격은 모든 출처를 합산</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -56334,11 +56330,16 @@
 끼니 규칙 축 문구 14개는 목표 축이 될 수 없다고 적혀 있었음</t>
   </si>
   <si>
-    <t>달력일자 시트에 설·추석 연휴 13일(2026 설 2/16~18 · 추석 9/24~26, 2027 설 2/5~8 · 추석 9/14~16)을 넣고, 명절·연휴 문구는 이 날짜에만 나온다
+    <t>달력일자 시트 2~14행 · 구현기준 R-03 · R-08 · R-10 · 검증규칙 V-39 · V-50 · 참조설정데이터 달력일자 시트</t>
+  </si>
+  <si>
+    <t>자동 노출 조건은 시간대, 평일·주말, 명절·연휴만 사용한다. 명절·연휴는 달력일자 시트의 날짜(calendar_code HOLIDAY)로 판정한다. 그 날짜에는 그날 목표 축에서 현재 단계 이하의 명절·연휴 문구가 통과하면 다른 문구보다 먼저 쓴다. 배달·편의점·회식·카페·사무실·급식·마트·야근·여행처럼 앱이 확인하지 않는 상황 조건은 사용하지 않는다.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>달력일자 시트에 설·추석 연휴 13일(2026 설 2/16~18 · 추석 9/24~26, 2027 설 2/5~8 · 추석 9/14~16)을 넣고, 명절·연휴 문구는 이 날짜에만 나오고, 그 날짜에는 다른 문구보다 먼저 쓴다
 끼니 규칙 축도 일반 축으로 본다: 그날 질문 축 · 직접 선택 연결 축에 통과 문구가 없을 때 끼니 규칙 축 문구가 후보가 된다</t>
-  </si>
-  <si>
-    <t>달력일자 시트 2~14행 · 구현기준 R-03 · R-08 · R-10 · 검증규칙 V-39 · V-50 · 참조설정데이터 달력일자 시트</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -61093,18 +61094,18 @@
         <v>2709</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="52">
+    <row r="22" spans="1:4" ht="65">
       <c r="A22" s="8" t="s">
+        <v>2731</v>
+      </c>
+      <c r="B22" s="8" t="s">
         <v>2732</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="C22" s="8" t="s">
+        <v>2735</v>
+      </c>
+      <c r="D22" s="8" t="s">
         <v>2733</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>2734</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>2735</v>
       </c>
     </row>
   </sheetData>
@@ -73382,7 +73383,7 @@
         <v>2452</v>
       </c>
       <c r="C39" s="29" t="s">
-        <v>2730</v>
+        <v>2729</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>2562</v>
@@ -73536,7 +73537,7 @@
         <v>2588</v>
       </c>
       <c r="C50" s="29" t="s">
-        <v>2731</v>
+        <v>2730</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>2589</v>
@@ -93647,7 +93648,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="37.5">
+    <row r="9" spans="1:7" ht="62.5">
       <c r="A9" s="6" t="s">
         <v>390</v>
       </c>
@@ -93661,7 +93662,7 @@
         <v>2469</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>2729</v>
+        <v>2734</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>2470</v>
@@ -95767,6 +95768,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x01010011BABF6A94C35643897AD108A63C3FA9" ma:contentTypeVersion="3" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="0dd8771f9317307737e3c0a6afa68b4c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="47def904-0df1-4aa1-ae40-c4bd318a6de7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8ccd85fd4a825fc66f8c3b5a4ab7306b" ns2:_="">
     <xsd:import namespace="47def904-0df1-4aa1-ae40-c4bd318a6de7"/>
@@ -95904,15 +95914,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA5F7BAD-F7AB-4266-8370-535EF14A9159}">
   <ds:schemaRefs>
@@ -95923,6 +95924,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE6123CC-E6A1-4739-AA75-207000A0601B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -95938,12 +95947,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>